--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567600</v>
+        <v>122567519</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577658</v>
+        <v>577659</v>
       </c>
       <c r="R2" t="n">
-        <v>7047696</v>
+        <v>7047666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122568871</v>
+        <v>122566515</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577847</v>
+        <v>577857</v>
       </c>
       <c r="R3" t="n">
-        <v>7047657</v>
+        <v>7047693</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122568013</v>
+        <v>122567603</v>
       </c>
       <c r="B4" t="n">
-        <v>90826</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +935,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577636</v>
+        <v>577640</v>
       </c>
       <c r="R4" t="n">
-        <v>7047783</v>
+        <v>7047712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,19 +1029,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567649</v>
+        <v>122567415</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1067,7 +1077,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577631</v>
+        <v>577665</v>
       </c>
       <c r="R5" t="n">
-        <v>7047709</v>
+        <v>7047625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122568098</v>
+        <v>122566494</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1198,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577684</v>
+        <v>577868</v>
       </c>
       <c r="R6" t="n">
-        <v>7047782</v>
+        <v>7047668</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,22 +1273,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122568123</v>
+        <v>122567426</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,27 +1301,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577688</v>
+        <v>577666</v>
       </c>
       <c r="R7" t="n">
-        <v>7047768</v>
+        <v>7047652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,12 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,19 +1394,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122568670</v>
+        <v>122568144</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1442,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577765</v>
+        <v>577721</v>
       </c>
       <c r="R8" t="n">
-        <v>7047696</v>
+        <v>7047806</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1507,19 +1516,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566696</v>
+        <v>122567856</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1555,7 +1564,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1564,10 +1573,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577752</v>
+        <v>577598</v>
       </c>
       <c r="R9" t="n">
-        <v>7047671</v>
+        <v>7047750</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1608,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1618,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1641,7 +1650,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566495</v>
+        <v>122566768</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1677,7 +1686,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1686,13 +1695,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577898</v>
+        <v>577712</v>
       </c>
       <c r="R10" t="n">
-        <v>7047638</v>
+        <v>7047643</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1721,7 +1730,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,12 +1740,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1751,22 +1760,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566643</v>
+        <v>122566471</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1779,34 +1788,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577816</v>
+        <v>577878</v>
       </c>
       <c r="R11" t="n">
-        <v>7047681</v>
+        <v>7047667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,7 +1852,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1848,7 +1862,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,22 +1882,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566485</v>
+        <v>122566643</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,39 +1910,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577908</v>
+        <v>577816</v>
       </c>
       <c r="R12" t="n">
-        <v>7047646</v>
+        <v>7047681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1955,7 +1969,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1965,12 +1979,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,7 +2006,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566494</v>
+        <v>122566694</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -2042,10 +2051,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577868</v>
+        <v>577770</v>
       </c>
       <c r="R13" t="n">
-        <v>7047668</v>
+        <v>7047663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2077,7 +2086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2087,12 +2096,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,7 +2128,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567856</v>
+        <v>122568123</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2164,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577598</v>
+        <v>577688</v>
       </c>
       <c r="R14" t="n">
-        <v>7047750</v>
+        <v>7047768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,7 +2208,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2209,7 +2218,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2241,7 +2250,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122568906</v>
+        <v>122567764</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2277,7 +2286,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2286,13 +2295,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577851</v>
+        <v>577641</v>
       </c>
       <c r="R15" t="n">
-        <v>7047625</v>
+        <v>7047789</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2321,7 +2330,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2331,12 +2340,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2363,10 +2367,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122568836</v>
+        <v>122567286</v>
       </c>
       <c r="B16" t="n">
-        <v>79737</v>
+        <v>90839</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,21 +2383,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2403,10 +2407,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577845</v>
+        <v>577696</v>
       </c>
       <c r="R16" t="n">
-        <v>7047652</v>
+        <v>7047629</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2438,7 +2442,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2448,7 +2452,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2461,14 +2465,24 @@
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567603</v>
+        <v>122568145</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,39 +2495,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577640</v>
+        <v>577696</v>
       </c>
       <c r="R17" t="n">
-        <v>7047712</v>
+        <v>7047755</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2545,7 +2554,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2555,12 +2564,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2575,22 +2579,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567426</v>
+        <v>122568906</v>
       </c>
       <c r="B18" t="n">
-        <v>90844</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2603,31 +2607,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577666</v>
+        <v>577851</v>
       </c>
       <c r="R18" t="n">
-        <v>7047652</v>
+        <v>7047625</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,7 +2681,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2708,10 +2713,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122568196</v>
+        <v>122568836</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2724,39 +2729,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577717</v>
+        <v>577845</v>
       </c>
       <c r="R19" t="n">
-        <v>7047745</v>
+        <v>7047652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2798,12 +2798,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2818,22 +2813,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122568941</v>
+        <v>122566271</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2846,27 +2841,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2875,13 +2870,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577874</v>
+        <v>577901</v>
       </c>
       <c r="R20" t="n">
-        <v>7047636</v>
+        <v>7047671</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2910,7 +2905,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2920,12 +2915,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2952,10 +2942,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568922</v>
+        <v>122568052</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2968,39 +2958,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577858</v>
+        <v>577647</v>
       </c>
       <c r="R21" t="n">
-        <v>7047635</v>
+        <v>7047774</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3032,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3042,12 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3060,11 +3040,21 @@
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567519</v>
+        <v>122566485</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -3109,10 +3099,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577659</v>
+        <v>577908</v>
       </c>
       <c r="R22" t="n">
-        <v>7047666</v>
+        <v>7047646</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3144,7 +3134,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3154,12 +3144,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3174,19 +3164,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566730</v>
+        <v>122567761</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -3231,10 +3221,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577749</v>
+        <v>577630</v>
       </c>
       <c r="R23" t="n">
-        <v>7047671</v>
+        <v>7047750</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3266,7 +3256,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3276,12 +3266,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,19 +3286,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567250</v>
+        <v>122567504</v>
       </c>
       <c r="B24" t="n">
         <v>57383</v>
@@ -3344,7 +3334,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3353,10 +3343,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577683</v>
+        <v>577648</v>
       </c>
       <c r="R24" t="n">
-        <v>7047626</v>
+        <v>7047682</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3388,7 +3378,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3398,7 +3388,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3418,12 +3408,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3433,7 +3423,7 @@
         <v>122565992</v>
       </c>
       <c r="B25" t="n">
-        <v>90844</v>
+        <v>90857</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3542,10 +3532,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122568145</v>
+        <v>122566730</v>
       </c>
       <c r="B26" t="n">
-        <v>90826</v>
+        <v>57383</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3558,34 +3548,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577696</v>
+        <v>577749</v>
       </c>
       <c r="R26" t="n">
-        <v>7047755</v>
+        <v>7047671</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3617,7 +3612,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3627,7 +3622,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,19 +3642,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566515</v>
+        <v>122566696</v>
       </c>
       <c r="B27" t="n">
         <v>57383</v>
@@ -3690,7 +3690,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577857</v>
+        <v>577752</v>
       </c>
       <c r="R27" t="n">
-        <v>7047693</v>
+        <v>7047671</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3762,14 +3762,24 @@
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567115</v>
+        <v>122568196</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3782,34 +3792,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577719</v>
+        <v>577717</v>
       </c>
       <c r="R28" t="n">
-        <v>7047669</v>
+        <v>7047745</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3841,7 +3856,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3851,7 +3866,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3866,19 +3886,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567764</v>
+        <v>122568871</v>
       </c>
       <c r="B29" t="n">
         <v>57383</v>
@@ -3914,7 +3934,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3923,13 +3943,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577641</v>
+        <v>577847</v>
       </c>
       <c r="R29" t="n">
-        <v>7047789</v>
+        <v>7047657</v>
       </c>
       <c r="S29" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3958,7 +3978,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3968,7 +3988,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3995,7 +4020,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122568234</v>
+        <v>122566495</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -4040,13 +4065,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577772</v>
+        <v>577898</v>
       </c>
       <c r="R30" t="n">
-        <v>7047747</v>
+        <v>7047638</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4075,7 +4100,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4085,7 +4110,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4117,10 +4142,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566508</v>
+        <v>122567250</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4133,34 +4158,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577875</v>
+        <v>577683</v>
       </c>
       <c r="R31" t="n">
-        <v>7047661</v>
+        <v>7047626</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4192,7 +4222,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4202,7 +4232,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4217,22 +4252,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566471</v>
+        <v>122568013</v>
       </c>
       <c r="B32" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4245,39 +4280,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577878</v>
+        <v>577636</v>
       </c>
       <c r="R32" t="n">
-        <v>7047667</v>
+        <v>7047783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4309,7 +4339,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4319,12 +4349,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4351,10 +4376,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566271</v>
+        <v>122568120</v>
       </c>
       <c r="B33" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4367,27 +4392,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4396,13 +4421,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577901</v>
+        <v>577697</v>
       </c>
       <c r="R33" t="n">
-        <v>7047671</v>
+        <v>7047768</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4431,7 +4456,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4441,7 +4466,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4468,10 +4498,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567965</v>
+        <v>122567649</v>
       </c>
       <c r="B34" t="n">
-        <v>90826</v>
+        <v>57383</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4484,34 +4514,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577621</v>
+        <v>577631</v>
       </c>
       <c r="R34" t="n">
-        <v>7047786</v>
+        <v>7047709</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4543,7 +4578,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4553,7 +4588,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4580,7 +4620,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566768</v>
+        <v>122568922</v>
       </c>
       <c r="B35" t="n">
         <v>57383</v>
@@ -4616,7 +4656,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4625,10 +4665,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577712</v>
+        <v>577858</v>
       </c>
       <c r="R35" t="n">
-        <v>7047643</v>
+        <v>7047635</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4660,7 +4700,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4670,7 +4710,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4690,19 +4730,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122568120</v>
+        <v>122568098</v>
       </c>
       <c r="B36" t="n">
         <v>57383</v>
@@ -4747,10 +4787,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577697</v>
+        <v>577684</v>
       </c>
       <c r="R36" t="n">
-        <v>7047768</v>
+        <v>7047782</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4782,7 +4822,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4792,12 +4832,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på två tallar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4812,19 +4852,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567761</v>
+        <v>122568941</v>
       </c>
       <c r="B37" t="n">
         <v>57383</v>
@@ -4869,10 +4909,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577630</v>
+        <v>577874</v>
       </c>
       <c r="R37" t="n">
-        <v>7047750</v>
+        <v>7047636</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4904,7 +4944,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4914,7 +4954,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4932,11 +4972,21 @@
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567415</v>
+        <v>122567600</v>
       </c>
       <c r="B38" t="n">
         <v>57383</v>
@@ -4972,7 +5022,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4981,10 +5031,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577665</v>
+        <v>577658</v>
       </c>
       <c r="R38" t="n">
-        <v>7047625</v>
+        <v>7047696</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5016,7 +5066,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5026,12 +5076,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5046,19 +5096,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122568144</v>
+        <v>122568670</v>
       </c>
       <c r="B39" t="n">
         <v>57383</v>
@@ -5103,10 +5153,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577721</v>
+        <v>577765</v>
       </c>
       <c r="R39" t="n">
-        <v>7047806</v>
+        <v>7047696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5138,7 +5188,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5148,7 +5198,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5168,22 +5218,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122568052</v>
+        <v>122568234</v>
       </c>
       <c r="B40" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5196,34 +5246,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577647</v>
+        <v>577772</v>
       </c>
       <c r="R40" t="n">
-        <v>7047774</v>
+        <v>7047747</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5255,7 +5310,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5265,7 +5320,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5280,22 +5340,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566694</v>
+        <v>122566508</v>
       </c>
       <c r="B41" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5308,39 +5368,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577770</v>
+        <v>577875</v>
       </c>
       <c r="R41" t="n">
-        <v>7047663</v>
+        <v>7047661</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5372,7 +5427,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5382,12 +5437,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5402,22 +5452,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567286</v>
+        <v>122567115</v>
       </c>
       <c r="B42" t="n">
-        <v>90826</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5430,21 +5480,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5454,10 +5504,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577696</v>
+        <v>577719</v>
       </c>
       <c r="R42" t="n">
-        <v>7047629</v>
+        <v>7047669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5489,7 +5539,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5499,7 +5549,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5526,10 +5576,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567504</v>
+        <v>122567965</v>
       </c>
       <c r="B43" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5542,39 +5592,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577648</v>
+        <v>577621</v>
       </c>
       <c r="R43" t="n">
-        <v>7047682</v>
+        <v>7047786</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5606,7 +5651,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5616,12 +5661,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567519</v>
+        <v>122568145</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577659</v>
+        <v>577696</v>
       </c>
       <c r="R2" t="n">
-        <v>7047666</v>
+        <v>7047755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566515</v>
+        <v>122568836</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577857</v>
+        <v>577845</v>
       </c>
       <c r="R3" t="n">
-        <v>7047693</v>
+        <v>7047652</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567603</v>
+        <v>122567426</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,27 +915,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577640</v>
+        <v>577666</v>
       </c>
       <c r="R4" t="n">
-        <v>7047712</v>
+        <v>7047652</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,19 +1008,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567415</v>
+        <v>122567856</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1077,7 +1056,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577665</v>
+        <v>577598</v>
       </c>
       <c r="R5" t="n">
-        <v>7047625</v>
+        <v>7047750</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566494</v>
+        <v>122568941</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1208,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577868</v>
+        <v>577874</v>
       </c>
       <c r="R6" t="n">
-        <v>7047668</v>
+        <v>7047636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567426</v>
+        <v>122566485</v>
       </c>
       <c r="B7" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,31 +1280,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577666</v>
+        <v>577908</v>
       </c>
       <c r="R7" t="n">
-        <v>7047652</v>
+        <v>7047646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,19 +1374,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122568144</v>
+        <v>122567600</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1451,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577721</v>
+        <v>577658</v>
       </c>
       <c r="R8" t="n">
-        <v>7047806</v>
+        <v>7047696</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1516,19 +1496,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567856</v>
+        <v>122568196</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1573,10 +1553,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577598</v>
+        <v>577717</v>
       </c>
       <c r="R9" t="n">
-        <v>7047750</v>
+        <v>7047745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1618,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1638,19 +1618,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566768</v>
+        <v>122566495</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1686,7 +1666,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1695,13 +1675,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577712</v>
+        <v>577898</v>
       </c>
       <c r="R10" t="n">
-        <v>7047643</v>
+        <v>7047638</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1730,7 +1710,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1740,12 +1720,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,19 +1740,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566471</v>
+        <v>122568144</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1817,10 +1797,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577878</v>
+        <v>577721</v>
       </c>
       <c r="R11" t="n">
-        <v>7047667</v>
+        <v>7047806</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1852,7 +1832,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1862,12 +1842,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,22 +1862,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566643</v>
+        <v>122568906</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,34 +1890,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577816</v>
+        <v>577851</v>
       </c>
       <c r="R12" t="n">
-        <v>7047681</v>
+        <v>7047625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1969,7 +1954,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1979,7 +1964,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,19 +1984,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566694</v>
+        <v>122567761</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -2051,10 +2041,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577770</v>
+        <v>577630</v>
       </c>
       <c r="R13" t="n">
-        <v>7047663</v>
+        <v>7047750</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,7 +2076,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,12 +2086,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,19 +2106,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122568123</v>
+        <v>122566494</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2173,10 +2163,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577688</v>
+        <v>577868</v>
       </c>
       <c r="R14" t="n">
-        <v>7047768</v>
+        <v>7047668</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,7 +2198,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2218,12 +2208,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,22 +2228,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567764</v>
+        <v>122566643</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2266,42 +2256,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577641</v>
+        <v>577816</v>
       </c>
       <c r="R15" t="n">
-        <v>7047789</v>
+        <v>7047681</v>
       </c>
       <c r="S15" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2330,7 +2315,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2340,7 +2325,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,22 +2340,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567286</v>
+        <v>122566768</v>
       </c>
       <c r="B16" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2383,34 +2368,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577696</v>
+        <v>577712</v>
       </c>
       <c r="R16" t="n">
-        <v>7047629</v>
+        <v>7047643</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2442,7 +2432,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2452,7 +2442,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2467,22 +2462,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122568145</v>
+        <v>122566694</v>
       </c>
       <c r="B17" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,34 +2490,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577696</v>
+        <v>577770</v>
       </c>
       <c r="R17" t="n">
-        <v>7047755</v>
+        <v>7047663</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2564,7 +2564,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2591,10 +2596,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122568906</v>
+        <v>122567286</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,39 +2612,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577851</v>
+        <v>577696</v>
       </c>
       <c r="R18" t="n">
-        <v>7047625</v>
+        <v>7047629</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,12 +2681,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2701,22 +2696,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122568836</v>
+        <v>122566271</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
+        <v>57536</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2729,37 +2724,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577845</v>
+        <v>577901</v>
       </c>
       <c r="R19" t="n">
-        <v>7047652</v>
+        <v>7047671</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,22 +2813,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566271</v>
+        <v>122568052</v>
       </c>
       <c r="B20" t="n">
-        <v>57536</v>
+        <v>79737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,42 +2841,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577901</v>
+        <v>577647</v>
       </c>
       <c r="R20" t="n">
-        <v>7047671</v>
+        <v>7047774</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2905,7 +2900,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2915,7 +2910,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568052</v>
+        <v>122568120</v>
       </c>
       <c r="B21" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2958,34 +2953,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577647</v>
+        <v>577697</v>
       </c>
       <c r="R21" t="n">
-        <v>7047774</v>
+        <v>7047768</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,10 +3059,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566485</v>
+        <v>122566508</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3070,39 +3075,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577908</v>
+        <v>577875</v>
       </c>
       <c r="R22" t="n">
-        <v>7047646</v>
+        <v>7047661</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3144,12 +3144,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3176,7 +3171,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567761</v>
+        <v>122567649</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -3221,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577630</v>
+        <v>577631</v>
       </c>
       <c r="R23" t="n">
-        <v>7047750</v>
+        <v>7047709</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3256,7 +3251,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3266,12 +3261,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3286,19 +3281,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567504</v>
+        <v>122567603</v>
       </c>
       <c r="B24" t="n">
         <v>57383</v>
@@ -3343,10 +3338,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577648</v>
+        <v>577640</v>
       </c>
       <c r="R24" t="n">
-        <v>7047682</v>
+        <v>7047712</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3378,7 +3373,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3388,7 +3383,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3420,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122565992</v>
+        <v>122567250</v>
       </c>
       <c r="B25" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3436,34 +3431,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577930</v>
+        <v>577683</v>
       </c>
       <c r="R25" t="n">
-        <v>7047678</v>
+        <v>7047626</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3505,7 +3505,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3532,7 +3537,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566730</v>
+        <v>122566471</v>
       </c>
       <c r="B26" t="n">
         <v>57383</v>
@@ -3577,10 +3582,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577749</v>
+        <v>577878</v>
       </c>
       <c r="R26" t="n">
-        <v>7047671</v>
+        <v>7047667</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3612,7 +3617,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3622,12 +3627,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,19 +3647,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566696</v>
+        <v>122568922</v>
       </c>
       <c r="B27" t="n">
         <v>57383</v>
@@ -3690,7 +3695,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3699,10 +3704,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577752</v>
+        <v>577858</v>
       </c>
       <c r="R27" t="n">
-        <v>7047671</v>
+        <v>7047635</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3734,7 +3739,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3744,12 +3749,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3764,19 +3769,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122568196</v>
+        <v>122567504</v>
       </c>
       <c r="B28" t="n">
         <v>57383</v>
@@ -3821,10 +3826,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577717</v>
+        <v>577648</v>
       </c>
       <c r="R28" t="n">
-        <v>7047745</v>
+        <v>7047682</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3856,7 +3861,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3866,7 +3871,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3886,19 +3891,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122568871</v>
+        <v>122568670</v>
       </c>
       <c r="B29" t="n">
         <v>57383</v>
@@ -3943,10 +3948,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577847</v>
+        <v>577765</v>
       </c>
       <c r="R29" t="n">
-        <v>7047657</v>
+        <v>7047696</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3978,7 +3983,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3988,12 +3993,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4020,7 +4025,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566495</v>
+        <v>122566730</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -4065,13 +4070,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577898</v>
+        <v>577749</v>
       </c>
       <c r="R30" t="n">
-        <v>7047638</v>
+        <v>7047671</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4100,7 +4105,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4110,7 +4115,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4142,7 +4147,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567250</v>
+        <v>122568123</v>
       </c>
       <c r="B31" t="n">
         <v>57383</v>
@@ -4178,7 +4183,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4187,10 +4192,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577683</v>
+        <v>577688</v>
       </c>
       <c r="R31" t="n">
-        <v>7047626</v>
+        <v>7047768</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4222,7 +4227,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4232,7 +4237,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4252,12 +4257,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4376,7 +4381,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122568120</v>
+        <v>122567764</v>
       </c>
       <c r="B33" t="n">
         <v>57383</v>
@@ -4412,7 +4417,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4421,13 +4426,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577697</v>
+        <v>577641</v>
       </c>
       <c r="R33" t="n">
-        <v>7047768</v>
+        <v>7047789</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4456,7 +4461,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4466,12 +4471,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på två tallar</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4498,7 +4498,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567649</v>
+        <v>122567519</v>
       </c>
       <c r="B34" t="n">
         <v>57383</v>
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577631</v>
+        <v>577659</v>
       </c>
       <c r="R34" t="n">
-        <v>7047709</v>
+        <v>7047666</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4608,19 +4608,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122568922</v>
+        <v>122566696</v>
       </c>
       <c r="B35" t="n">
         <v>57383</v>
@@ -4656,7 +4656,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577858</v>
+        <v>577752</v>
       </c>
       <c r="R35" t="n">
-        <v>7047635</v>
+        <v>7047671</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4730,22 +4730,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122568098</v>
+        <v>122567965</v>
       </c>
       <c r="B36" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4758,39 +4758,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577684</v>
+        <v>577621</v>
       </c>
       <c r="R36" t="n">
-        <v>7047782</v>
+        <v>7047786</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4822,7 +4817,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4832,12 +4827,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4864,7 +4854,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122568941</v>
+        <v>122568098</v>
       </c>
       <c r="B37" t="n">
         <v>57383</v>
@@ -4909,10 +4899,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577874</v>
+        <v>577684</v>
       </c>
       <c r="R37" t="n">
-        <v>7047636</v>
+        <v>7047782</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4944,7 +4934,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4954,12 +4944,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4974,19 +4964,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567600</v>
+        <v>122568234</v>
       </c>
       <c r="B38" t="n">
         <v>57383</v>
@@ -5031,10 +5021,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577658</v>
+        <v>577772</v>
       </c>
       <c r="R38" t="n">
-        <v>7047696</v>
+        <v>7047747</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5066,7 +5056,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5076,7 +5066,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5096,19 +5086,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122568670</v>
+        <v>122567415</v>
       </c>
       <c r="B39" t="n">
         <v>57383</v>
@@ -5144,7 +5134,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5153,10 +5143,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577765</v>
+        <v>577665</v>
       </c>
       <c r="R39" t="n">
-        <v>7047696</v>
+        <v>7047625</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5188,7 +5178,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5198,12 +5188,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5218,22 +5208,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122568234</v>
+        <v>122565992</v>
       </c>
       <c r="B40" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5246,39 +5236,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577772</v>
+        <v>577930</v>
       </c>
       <c r="R40" t="n">
-        <v>7047747</v>
+        <v>7047678</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5310,7 +5295,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5320,12 +5305,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5340,22 +5320,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566508</v>
+        <v>122568871</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5368,34 +5348,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577875</v>
+        <v>577847</v>
       </c>
       <c r="R41" t="n">
-        <v>7047661</v>
+        <v>7047657</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5427,7 +5412,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5437,7 +5422,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5452,12 +5442,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5576,10 +5566,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567965</v>
+        <v>122566515</v>
       </c>
       <c r="B43" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5592,34 +5582,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577621</v>
+        <v>577857</v>
       </c>
       <c r="R43" t="n">
-        <v>7047786</v>
+        <v>7047693</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5651,7 +5646,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5661,7 +5656,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5676,12 +5676,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122568145</v>
+        <v>122568836</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
+        <v>79737</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577696</v>
+        <v>577845</v>
       </c>
       <c r="R2" t="n">
-        <v>7047755</v>
+        <v>7047652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122568836</v>
+        <v>122568145</v>
       </c>
       <c r="B3" t="n">
-        <v>79737</v>
+        <v>90839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577845</v>
+        <v>577696</v>
       </c>
       <c r="R3" t="n">
-        <v>7047652</v>
+        <v>7047755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567761</v>
+        <v>122566643</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,39 +2012,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577630</v>
+        <v>577816</v>
       </c>
       <c r="R13" t="n">
-        <v>7047750</v>
+        <v>7047681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,7 +2071,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2086,12 +2081,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2106,19 +2096,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566494</v>
+        <v>122567761</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2163,10 +2153,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577868</v>
+        <v>577630</v>
       </c>
       <c r="R14" t="n">
-        <v>7047668</v>
+        <v>7047750</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2198,7 +2188,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2208,7 +2198,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2228,22 +2218,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566643</v>
+        <v>122566494</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2256,34 +2246,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577816</v>
+        <v>577868</v>
       </c>
       <c r="R15" t="n">
-        <v>7047681</v>
+        <v>7047668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2315,7 +2310,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2325,7 +2320,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2340,22 +2340,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566768</v>
+        <v>122567286</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2368,39 +2368,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577712</v>
+        <v>577696</v>
       </c>
       <c r="R16" t="n">
-        <v>7047643</v>
+        <v>7047629</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2432,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2442,12 +2437,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,19 +2452,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566694</v>
+        <v>122566768</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2510,7 +2500,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2519,10 +2509,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577770</v>
+        <v>577712</v>
       </c>
       <c r="R17" t="n">
-        <v>7047663</v>
+        <v>7047643</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2554,7 +2544,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2564,12 +2554,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2596,10 +2586,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567286</v>
+        <v>122566694</v>
       </c>
       <c r="B18" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2612,34 +2602,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577696</v>
+        <v>577770</v>
       </c>
       <c r="R18" t="n">
-        <v>7047629</v>
+        <v>7047663</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2666,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,7 +2676,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,12 +2696,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122568052</v>
+        <v>122568120</v>
       </c>
       <c r="B20" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,34 +2841,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577647</v>
+        <v>577697</v>
       </c>
       <c r="R20" t="n">
-        <v>7047774</v>
+        <v>7047768</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2900,7 +2905,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2910,7 +2915,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,10 +2947,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568120</v>
+        <v>122568052</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2953,39 +2963,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577697</v>
+        <v>577647</v>
       </c>
       <c r="R21" t="n">
-        <v>7047768</v>
+        <v>7047774</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3017,7 +3022,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,12 +3032,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på två tallar</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122568836</v>
+        <v>122566768</v>
       </c>
       <c r="B2" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577845</v>
+        <v>577712</v>
       </c>
       <c r="R2" t="n">
-        <v>7047652</v>
+        <v>7047643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122568145</v>
+        <v>122567649</v>
       </c>
       <c r="B3" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577696</v>
+        <v>577631</v>
       </c>
       <c r="R3" t="n">
-        <v>7047755</v>
+        <v>7047709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567426</v>
+        <v>122567250</v>
       </c>
       <c r="B4" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,31 +935,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -948,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577666</v>
+        <v>577683</v>
       </c>
       <c r="R4" t="n">
-        <v>7047652</v>
+        <v>7047626</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567856</v>
+        <v>122565992</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,39 +1057,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577598</v>
+        <v>577930</v>
       </c>
       <c r="R5" t="n">
-        <v>7047750</v>
+        <v>7047678</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122568941</v>
+        <v>122567286</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>90833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,39 +1169,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577874</v>
+        <v>577696</v>
       </c>
       <c r="R6" t="n">
-        <v>7047636</v>
+        <v>7047629</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,19 +1253,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566485</v>
+        <v>122567603</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1309,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577908</v>
+        <v>577640</v>
       </c>
       <c r="R7" t="n">
-        <v>7047646</v>
+        <v>7047712</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567600</v>
+        <v>122566508</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,39 +1403,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577658</v>
+        <v>577875</v>
       </c>
       <c r="R8" t="n">
-        <v>7047696</v>
+        <v>7047661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,12 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,19 +1487,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122568196</v>
+        <v>122568144</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1553,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577717</v>
+        <v>577721</v>
       </c>
       <c r="R9" t="n">
-        <v>7047745</v>
+        <v>7047806</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1618,19 +1609,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566495</v>
+        <v>122568670</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1675,13 +1666,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577898</v>
+        <v>577765</v>
       </c>
       <c r="R10" t="n">
-        <v>7047638</v>
+        <v>7047696</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1710,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1740,19 +1731,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122568144</v>
+        <v>122566515</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1797,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577721</v>
+        <v>577857</v>
       </c>
       <c r="R11" t="n">
-        <v>7047806</v>
+        <v>7047693</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1842,12 +1833,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,19 +1853,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122568906</v>
+        <v>122566694</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1919,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577851</v>
+        <v>577770</v>
       </c>
       <c r="R12" t="n">
-        <v>7047625</v>
+        <v>7047663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,12 +1955,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1996,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566643</v>
+        <v>122568098</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,34 +2003,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577816</v>
+        <v>577684</v>
       </c>
       <c r="R13" t="n">
-        <v>7047681</v>
+        <v>7047782</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2081,7 +2077,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,7 +2109,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567761</v>
+        <v>122568922</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2153,10 +2154,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577630</v>
+        <v>577858</v>
       </c>
       <c r="R14" t="n">
-        <v>7047750</v>
+        <v>7047635</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,7 +2189,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2198,7 +2199,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2230,7 +2231,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566494</v>
+        <v>122567600</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2275,10 +2276,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577868</v>
+        <v>577658</v>
       </c>
       <c r="R15" t="n">
-        <v>7047668</v>
+        <v>7047696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2320,12 +2321,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2352,10 +2353,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567286</v>
+        <v>122568196</v>
       </c>
       <c r="B16" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2368,34 +2369,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577696</v>
+        <v>577717</v>
       </c>
       <c r="R16" t="n">
-        <v>7047629</v>
+        <v>7047745</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,7 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,22 +2463,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566768</v>
+        <v>122566643</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2480,39 +2491,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577712</v>
+        <v>577816</v>
       </c>
       <c r="R17" t="n">
-        <v>7047643</v>
+        <v>7047681</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,7 +2550,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2554,12 +2560,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,22 +2575,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566694</v>
+        <v>122567965</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>90833</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2602,39 +2603,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577770</v>
+        <v>577621</v>
       </c>
       <c r="R18" t="n">
-        <v>7047663</v>
+        <v>7047786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,12 +2672,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,22 +2687,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566271</v>
+        <v>122568871</v>
       </c>
       <c r="B19" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2724,27 +2715,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2753,13 +2744,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577901</v>
+        <v>577847</v>
       </c>
       <c r="R19" t="n">
-        <v>7047671</v>
+        <v>7047657</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2788,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2798,7 +2789,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2825,7 +2821,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122568120</v>
+        <v>122567761</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2870,10 +2866,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577697</v>
+        <v>577630</v>
       </c>
       <c r="R20" t="n">
-        <v>7047768</v>
+        <v>7047750</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2905,7 +2901,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2915,12 +2911,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på två tallar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,22 +2931,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568052</v>
+        <v>122568123</v>
       </c>
       <c r="B21" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2963,34 +2959,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577647</v>
+        <v>577688</v>
       </c>
       <c r="R21" t="n">
-        <v>7047774</v>
+        <v>7047768</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,7 +3023,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3032,7 +3033,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3047,22 +3053,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566508</v>
+        <v>122567504</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3075,34 +3081,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577875</v>
+        <v>577648</v>
       </c>
       <c r="R22" t="n">
-        <v>7047661</v>
+        <v>7047682</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3134,7 +3145,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3144,7 +3155,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,7 +3187,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567649</v>
+        <v>122567856</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -3216,10 +3232,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577631</v>
+        <v>577598</v>
       </c>
       <c r="R23" t="n">
-        <v>7047709</v>
+        <v>7047750</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3251,7 +3267,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3261,7 +3277,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3293,10 +3309,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567603</v>
+        <v>122568145</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>90833</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3309,39 +3325,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577640</v>
+        <v>577696</v>
       </c>
       <c r="R24" t="n">
-        <v>7047712</v>
+        <v>7047755</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3373,7 +3384,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3383,12 +3394,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3403,22 +3409,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567250</v>
+        <v>122568052</v>
       </c>
       <c r="B25" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3431,39 +3437,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577683</v>
+        <v>577647</v>
       </c>
       <c r="R25" t="n">
-        <v>7047626</v>
+        <v>7047774</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3495,7 +3496,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3505,12 +3506,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3537,10 +3533,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566471</v>
+        <v>122568836</v>
       </c>
       <c r="B26" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3553,39 +3549,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577878</v>
+        <v>577845</v>
       </c>
       <c r="R26" t="n">
-        <v>7047667</v>
+        <v>7047652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3617,7 +3608,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3627,12 +3618,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3647,19 +3633,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122568922</v>
+        <v>122567415</v>
       </c>
       <c r="B27" t="n">
         <v>57383</v>
@@ -3695,7 +3681,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3704,10 +3690,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577858</v>
+        <v>577665</v>
       </c>
       <c r="R27" t="n">
-        <v>7047635</v>
+        <v>7047625</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3739,7 +3725,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3749,7 +3735,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3769,22 +3755,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567504</v>
+        <v>122568013</v>
       </c>
       <c r="B28" t="n">
-        <v>57383</v>
+        <v>90833</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3797,39 +3783,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577648</v>
+        <v>577636</v>
       </c>
       <c r="R28" t="n">
-        <v>7047682</v>
+        <v>7047783</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3861,7 +3842,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3871,12 +3852,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3891,19 +3867,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122568670</v>
+        <v>122566696</v>
       </c>
       <c r="B29" t="n">
         <v>57383</v>
@@ -3939,7 +3915,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3948,10 +3924,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577765</v>
+        <v>577752</v>
       </c>
       <c r="R29" t="n">
-        <v>7047696</v>
+        <v>7047671</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3983,7 +3959,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3993,7 +3969,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4013,12 +3989,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4147,7 +4123,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122568123</v>
+        <v>122566485</v>
       </c>
       <c r="B31" t="n">
         <v>57383</v>
@@ -4192,10 +4168,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577688</v>
+        <v>577908</v>
       </c>
       <c r="R31" t="n">
-        <v>7047768</v>
+        <v>7047646</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4227,7 +4203,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4237,12 +4213,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4269,10 +4245,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122568013</v>
+        <v>122568906</v>
       </c>
       <c r="B32" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4285,34 +4261,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577636</v>
+        <v>577851</v>
       </c>
       <c r="R32" t="n">
-        <v>7047783</v>
+        <v>7047625</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4344,7 +4325,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4354,7 +4335,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4381,10 +4367,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567764</v>
+        <v>122567115</v>
       </c>
       <c r="B33" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4397,42 +4383,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577641</v>
+        <v>577719</v>
       </c>
       <c r="R33" t="n">
-        <v>7047789</v>
+        <v>7047669</v>
       </c>
       <c r="S33" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4461,7 +4442,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4471,7 +4452,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4486,22 +4467,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567519</v>
+        <v>122567426</v>
       </c>
       <c r="B34" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4514,27 +4495,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4543,10 +4528,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577659</v>
+        <v>577666</v>
       </c>
       <c r="R34" t="n">
-        <v>7047666</v>
+        <v>7047652</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4578,7 +4563,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4588,12 +4573,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4620,7 +4600,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566696</v>
+        <v>122566471</v>
       </c>
       <c r="B35" t="n">
         <v>57383</v>
@@ -4656,7 +4636,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4665,10 +4645,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577752</v>
+        <v>577878</v>
       </c>
       <c r="R35" t="n">
-        <v>7047671</v>
+        <v>7047667</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4700,7 +4680,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4710,12 +4690,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4730,22 +4710,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567965</v>
+        <v>122568941</v>
       </c>
       <c r="B36" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4758,34 +4738,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577621</v>
+        <v>577874</v>
       </c>
       <c r="R36" t="n">
-        <v>7047786</v>
+        <v>7047636</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4817,7 +4802,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4827,7 +4812,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4842,19 +4832,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122568098</v>
+        <v>122568120</v>
       </c>
       <c r="B37" t="n">
         <v>57383</v>
@@ -4899,10 +4889,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577684</v>
+        <v>577697</v>
       </c>
       <c r="R37" t="n">
-        <v>7047782</v>
+        <v>7047768</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4934,7 +4924,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4944,12 +4934,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4964,19 +4954,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122568234</v>
+        <v>122567764</v>
       </c>
       <c r="B38" t="n">
         <v>57383</v>
@@ -5012,7 +5002,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5021,13 +5011,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577772</v>
+        <v>577641</v>
       </c>
       <c r="R38" t="n">
-        <v>7047747</v>
+        <v>7047789</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5056,7 +5046,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5066,12 +5056,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5086,22 +5071,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567415</v>
+        <v>122566271</v>
       </c>
       <c r="B39" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5114,27 +5099,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5143,13 +5128,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577665</v>
+        <v>577901</v>
       </c>
       <c r="R39" t="n">
-        <v>7047625</v>
+        <v>7047671</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5178,7 +5163,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5188,12 +5173,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5208,22 +5188,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122565992</v>
+        <v>122566495</v>
       </c>
       <c r="B40" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5236,37 +5216,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577930</v>
+        <v>577898</v>
       </c>
       <c r="R40" t="n">
-        <v>7047678</v>
+        <v>7047638</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5295,7 +5280,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5305,7 +5290,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5320,19 +5310,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122568871</v>
+        <v>122568234</v>
       </c>
       <c r="B41" t="n">
         <v>57383</v>
@@ -5377,10 +5367,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577847</v>
+        <v>577772</v>
       </c>
       <c r="R41" t="n">
-        <v>7047657</v>
+        <v>7047747</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5412,7 +5402,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5422,12 +5412,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,22 +5432,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567115</v>
+        <v>122566494</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5470,34 +5460,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577719</v>
+        <v>577868</v>
       </c>
       <c r="R42" t="n">
-        <v>7047669</v>
+        <v>7047668</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5529,7 +5524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5539,7 +5534,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5554,19 +5554,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566515</v>
+        <v>122567519</v>
       </c>
       <c r="B43" t="n">
         <v>57383</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577857</v>
+        <v>577659</v>
       </c>
       <c r="R43" t="n">
-        <v>7047693</v>
+        <v>7047666</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5676,12 +5676,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566768</v>
+        <v>122566694</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577712</v>
+        <v>577770</v>
       </c>
       <c r="R2" t="n">
-        <v>7047643</v>
+        <v>7047663</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567649</v>
+        <v>122568941</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577631</v>
+        <v>577874</v>
       </c>
       <c r="R3" t="n">
-        <v>7047709</v>
+        <v>7047636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567250</v>
+        <v>122568052</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577683</v>
+        <v>577647</v>
       </c>
       <c r="R4" t="n">
-        <v>7047626</v>
+        <v>7047774</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565992</v>
+        <v>122566508</v>
       </c>
       <c r="B5" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577930</v>
+        <v>577875</v>
       </c>
       <c r="R5" t="n">
-        <v>7047678</v>
+        <v>7047661</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,12 +1131,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1265,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567603</v>
+        <v>122566768</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1301,7 +1291,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1310,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577640</v>
+        <v>577712</v>
       </c>
       <c r="R7" t="n">
-        <v>7047712</v>
+        <v>7047643</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,22 +1365,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566508</v>
+        <v>122568906</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,34 +1393,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577875</v>
+        <v>577851</v>
       </c>
       <c r="R8" t="n">
-        <v>7047661</v>
+        <v>7047625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1467,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,19 +1487,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122568144</v>
+        <v>122567504</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577721</v>
+        <v>577648</v>
       </c>
       <c r="R9" t="n">
-        <v>7047806</v>
+        <v>7047682</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1621,7 +1621,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122568670</v>
+        <v>122568196</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577765</v>
+        <v>577717</v>
       </c>
       <c r="R10" t="n">
-        <v>7047696</v>
+        <v>7047745</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1743,7 +1743,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566515</v>
+        <v>122568922</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577857</v>
+        <v>577858</v>
       </c>
       <c r="R11" t="n">
-        <v>7047693</v>
+        <v>7047635</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1853,19 +1853,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566694</v>
+        <v>122566494</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577770</v>
+        <v>577868</v>
       </c>
       <c r="R12" t="n">
-        <v>7047663</v>
+        <v>7047668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,7 +1987,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122568098</v>
+        <v>122568234</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577684</v>
+        <v>577772</v>
       </c>
       <c r="R13" t="n">
-        <v>7047782</v>
+        <v>7047747</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2109,7 +2109,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122568922</v>
+        <v>122566485</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577858</v>
+        <v>577908</v>
       </c>
       <c r="R14" t="n">
-        <v>7047635</v>
+        <v>7047646</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2219,22 +2219,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567600</v>
+        <v>122567965</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>90833</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,39 +2247,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577658</v>
+        <v>577621</v>
       </c>
       <c r="R15" t="n">
-        <v>7047696</v>
+        <v>7047786</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,7 +2306,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,12 +2316,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2341,19 +2331,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122568196</v>
+        <v>122567761</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2398,10 +2388,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577717</v>
+        <v>577630</v>
       </c>
       <c r="R16" t="n">
-        <v>7047745</v>
+        <v>7047750</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2433,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2463,22 +2453,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566643</v>
+        <v>122567519</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2491,34 +2481,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577816</v>
+        <v>577659</v>
       </c>
       <c r="R17" t="n">
-        <v>7047681</v>
+        <v>7047666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2550,7 +2545,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2560,7 +2555,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2575,22 +2575,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567965</v>
+        <v>122567115</v>
       </c>
       <c r="B18" t="n">
-        <v>90833</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2603,21 +2603,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577621</v>
+        <v>577719</v>
       </c>
       <c r="R18" t="n">
-        <v>7047786</v>
+        <v>7047669</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2699,7 +2699,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122568871</v>
+        <v>122566471</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577847</v>
+        <v>577878</v>
       </c>
       <c r="R19" t="n">
-        <v>7047657</v>
+        <v>7047667</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2821,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567761</v>
+        <v>122568013</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>90833</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2837,39 +2837,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577630</v>
+        <v>577636</v>
       </c>
       <c r="R20" t="n">
-        <v>7047750</v>
+        <v>7047783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2901,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2911,12 +2906,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2931,19 +2921,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568123</v>
+        <v>122567603</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2988,10 +2978,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577688</v>
+        <v>577640</v>
       </c>
       <c r="R21" t="n">
-        <v>7047768</v>
+        <v>7047712</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3023,7 +3013,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3033,7 +3023,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3065,7 +3055,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567504</v>
+        <v>122567856</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -3110,10 +3100,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577648</v>
+        <v>577598</v>
       </c>
       <c r="R22" t="n">
-        <v>7047682</v>
+        <v>7047750</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,7 +3135,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3155,7 +3145,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3187,7 +3177,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567856</v>
+        <v>122567415</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -3223,7 +3213,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3232,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577598</v>
+        <v>577665</v>
       </c>
       <c r="R23" t="n">
-        <v>7047750</v>
+        <v>7047625</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3267,7 +3257,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3277,12 +3267,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3421,10 +3411,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122568052</v>
+        <v>122568144</v>
       </c>
       <c r="B25" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3437,34 +3427,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577647</v>
+        <v>577721</v>
       </c>
       <c r="R25" t="n">
-        <v>7047774</v>
+        <v>7047806</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3496,7 +3491,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3506,7 +3501,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3521,22 +3521,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122568836</v>
+        <v>122566730</v>
       </c>
       <c r="B26" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3549,34 +3549,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577845</v>
+        <v>577749</v>
       </c>
       <c r="R26" t="n">
-        <v>7047652</v>
+        <v>7047671</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3608,7 +3613,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3618,7 +3623,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3633,19 +3643,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567415</v>
+        <v>122568670</v>
       </c>
       <c r="B27" t="n">
         <v>57383</v>
@@ -3681,7 +3691,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3690,10 +3700,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577665</v>
+        <v>577765</v>
       </c>
       <c r="R27" t="n">
-        <v>7047625</v>
+        <v>7047696</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3725,7 +3735,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3735,12 +3745,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3755,22 +3765,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122568013</v>
+        <v>122566495</v>
       </c>
       <c r="B28" t="n">
-        <v>90833</v>
+        <v>57383</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3783,37 +3793,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577636</v>
+        <v>577898</v>
       </c>
       <c r="R28" t="n">
-        <v>7047783</v>
+        <v>7047638</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3842,7 +3857,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3852,7 +3867,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3867,19 +3887,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566696</v>
+        <v>122566515</v>
       </c>
       <c r="B29" t="n">
         <v>57383</v>
@@ -3915,7 +3935,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3924,10 +3944,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577752</v>
+        <v>577857</v>
       </c>
       <c r="R29" t="n">
-        <v>7047671</v>
+        <v>7047693</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3959,7 +3979,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3969,12 +3989,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3989,19 +4009,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566730</v>
+        <v>122568120</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -4046,10 +4066,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577749</v>
+        <v>577697</v>
       </c>
       <c r="R30" t="n">
-        <v>7047671</v>
+        <v>7047768</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4081,7 +4101,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4091,12 +4111,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4111,19 +4131,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566485</v>
+        <v>122567600</v>
       </c>
       <c r="B31" t="n">
         <v>57383</v>
@@ -4168,10 +4188,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577908</v>
+        <v>577658</v>
       </c>
       <c r="R31" t="n">
-        <v>7047646</v>
+        <v>7047696</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4203,7 +4223,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4213,12 +4233,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4233,19 +4253,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122568906</v>
+        <v>122567250</v>
       </c>
       <c r="B32" t="n">
         <v>57383</v>
@@ -4281,7 +4301,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4290,10 +4310,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577851</v>
+        <v>577683</v>
       </c>
       <c r="R32" t="n">
-        <v>7047625</v>
+        <v>7047626</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4325,7 +4345,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4335,12 +4355,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4367,10 +4387,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567115</v>
+        <v>122566271</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4383,37 +4403,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577719</v>
+        <v>577901</v>
       </c>
       <c r="R33" t="n">
-        <v>7047669</v>
+        <v>7047671</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4442,7 +4467,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4452,7 +4477,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4467,12 +4492,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4600,7 +4625,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566471</v>
+        <v>122567649</v>
       </c>
       <c r="B35" t="n">
         <v>57383</v>
@@ -4645,10 +4670,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577878</v>
+        <v>577631</v>
       </c>
       <c r="R35" t="n">
-        <v>7047667</v>
+        <v>7047709</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4680,7 +4705,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4690,12 +4715,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4710,19 +4735,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122568941</v>
+        <v>122568871</v>
       </c>
       <c r="B36" t="n">
         <v>57383</v>
@@ -4767,10 +4792,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577874</v>
+        <v>577847</v>
       </c>
       <c r="R36" t="n">
-        <v>7047636</v>
+        <v>7047657</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4802,7 +4827,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4812,7 +4837,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4844,7 +4869,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122568120</v>
+        <v>122567764</v>
       </c>
       <c r="B37" t="n">
         <v>57383</v>
@@ -4880,7 +4905,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4889,13 +4914,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577697</v>
+        <v>577641</v>
       </c>
       <c r="R37" t="n">
-        <v>7047768</v>
+        <v>7047789</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4924,7 +4949,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4934,12 +4959,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på två tallar</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4966,10 +4986,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567764</v>
+        <v>122566643</v>
       </c>
       <c r="B38" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4982,42 +5002,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577641</v>
+        <v>577816</v>
       </c>
       <c r="R38" t="n">
-        <v>7047789</v>
+        <v>7047681</v>
       </c>
       <c r="S38" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5046,7 +5061,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5056,7 +5071,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5071,22 +5086,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566271</v>
+        <v>122568098</v>
       </c>
       <c r="B39" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5099,27 +5114,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5128,13 +5143,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577901</v>
+        <v>577684</v>
       </c>
       <c r="R39" t="n">
-        <v>7047671</v>
+        <v>7047782</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5163,7 +5178,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5173,7 +5188,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5188,22 +5208,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566495</v>
+        <v>122565992</v>
       </c>
       <c r="B40" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5216,42 +5236,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577898</v>
+        <v>577930</v>
       </c>
       <c r="R40" t="n">
-        <v>7047638</v>
+        <v>7047678</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5280,7 +5295,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5290,12 +5305,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5310,19 +5320,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122568234</v>
+        <v>122568123</v>
       </c>
       <c r="B41" t="n">
         <v>57383</v>
@@ -5367,10 +5377,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577772</v>
+        <v>577688</v>
       </c>
       <c r="R41" t="n">
-        <v>7047747</v>
+        <v>7047768</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5402,7 +5412,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5412,7 +5422,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5444,7 +5454,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566494</v>
+        <v>122566696</v>
       </c>
       <c r="B42" t="n">
         <v>57383</v>
@@ -5480,7 +5490,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5489,10 +5499,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577868</v>
+        <v>577752</v>
       </c>
       <c r="R42" t="n">
-        <v>7047668</v>
+        <v>7047671</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5524,7 +5534,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5534,12 +5544,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5554,22 +5564,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567519</v>
+        <v>122568836</v>
       </c>
       <c r="B43" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5582,39 +5592,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577659</v>
+        <v>577845</v>
       </c>
       <c r="R43" t="n">
-        <v>7047666</v>
+        <v>7047652</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5646,7 +5651,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5656,12 +5661,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5676,12 +5676,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566694</v>
+        <v>122568670</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577770</v>
+        <v>577765</v>
       </c>
       <c r="R2" t="n">
-        <v>7047663</v>
+        <v>7047696</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122568941</v>
+        <v>122568922</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577874</v>
+        <v>577858</v>
       </c>
       <c r="R3" t="n">
-        <v>7047636</v>
+        <v>7047635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122568052</v>
+        <v>122568871</v>
       </c>
       <c r="B4" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +935,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577647</v>
+        <v>577847</v>
       </c>
       <c r="R4" t="n">
-        <v>7047774</v>
+        <v>7047657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566508</v>
+        <v>122567519</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1057,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577875</v>
+        <v>577659</v>
       </c>
       <c r="R5" t="n">
-        <v>7047661</v>
+        <v>7047666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1151,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567286</v>
+        <v>122568234</v>
       </c>
       <c r="B6" t="n">
-        <v>90833</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1179,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577696</v>
+        <v>577772</v>
       </c>
       <c r="R6" t="n">
-        <v>7047629</v>
+        <v>7047747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566768</v>
+        <v>122567856</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,7 +1321,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1300,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577712</v>
+        <v>577598</v>
       </c>
       <c r="R7" t="n">
-        <v>7047643</v>
+        <v>7047750</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1375,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,22 +1395,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122568906</v>
+        <v>122567286</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>90834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,39 +1423,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577851</v>
+        <v>577696</v>
       </c>
       <c r="R8" t="n">
-        <v>7047625</v>
+        <v>7047629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,12 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,22 +1507,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567504</v>
+        <v>122566471</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1544,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577648</v>
+        <v>577878</v>
       </c>
       <c r="R9" t="n">
-        <v>7047682</v>
+        <v>7047667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,12 +1609,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,22 +1629,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122568196</v>
+        <v>122568145</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>90834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,39 +1657,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577717</v>
+        <v>577696</v>
       </c>
       <c r="R10" t="n">
-        <v>7047745</v>
+        <v>7047755</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,12 +1726,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122568922</v>
+        <v>122567115</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,39 +1769,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577858</v>
+        <v>577719</v>
       </c>
       <c r="R11" t="n">
-        <v>7047635</v>
+        <v>7047669</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,12 +1838,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,22 +1853,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566494</v>
+        <v>122568144</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577868</v>
+        <v>577721</v>
       </c>
       <c r="R12" t="n">
-        <v>7047668</v>
+        <v>7047806</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,22 +1975,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122568234</v>
+        <v>122567504</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577772</v>
+        <v>577648</v>
       </c>
       <c r="R13" t="n">
-        <v>7047747</v>
+        <v>7047682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2109,10 +2109,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566485</v>
+        <v>122567649</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577908</v>
+        <v>577631</v>
       </c>
       <c r="R14" t="n">
-        <v>7047646</v>
+        <v>7047709</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,10 +2231,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567965</v>
+        <v>122568013</v>
       </c>
       <c r="B15" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577621</v>
+        <v>577636</v>
       </c>
       <c r="R15" t="n">
-        <v>7047786</v>
+        <v>7047783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,22 +2331,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567761</v>
+        <v>122566508</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2359,39 +2359,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577630</v>
+        <v>577875</v>
       </c>
       <c r="R16" t="n">
-        <v>7047750</v>
+        <v>7047661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2423,7 +2418,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2433,12 +2428,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2453,22 +2443,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567519</v>
+        <v>122566768</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2501,7 +2491,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2510,10 +2500,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577659</v>
+        <v>577712</v>
       </c>
       <c r="R17" t="n">
-        <v>7047666</v>
+        <v>7047643</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2545,7 +2535,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2555,12 +2545,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2587,10 +2577,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567115</v>
+        <v>122567426</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2603,34 +2593,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577719</v>
+        <v>577666</v>
       </c>
       <c r="R18" t="n">
-        <v>7047669</v>
+        <v>7047652</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2661,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,7 +2671,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2687,22 +2686,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566471</v>
+        <v>122568120</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2744,10 +2743,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577878</v>
+        <v>577697</v>
       </c>
       <c r="R19" t="n">
-        <v>7047667</v>
+        <v>7047768</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2788,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2821,10 +2820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122568013</v>
+        <v>122567764</v>
       </c>
       <c r="B20" t="n">
-        <v>90833</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2837,37 +2836,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577636</v>
+        <v>577641</v>
       </c>
       <c r="R20" t="n">
-        <v>7047783</v>
+        <v>7047789</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2896,7 +2900,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2906,7 +2910,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2933,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567603</v>
+        <v>122568196</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2978,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577640</v>
+        <v>577717</v>
       </c>
       <c r="R21" t="n">
-        <v>7047712</v>
+        <v>7047745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3013,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3023,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3043,22 +3047,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567856</v>
+        <v>122566485</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3100,10 +3104,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577598</v>
+        <v>577908</v>
       </c>
       <c r="R22" t="n">
-        <v>7047750</v>
+        <v>7047646</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3135,7 +3139,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3145,12 +3149,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3177,10 +3181,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567415</v>
+        <v>122566494</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3213,7 +3217,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3222,10 +3226,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577665</v>
+        <v>577868</v>
       </c>
       <c r="R23" t="n">
-        <v>7047625</v>
+        <v>7047668</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3257,7 +3261,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3267,7 +3271,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3287,22 +3291,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122568145</v>
+        <v>122568906</v>
       </c>
       <c r="B24" t="n">
-        <v>90833</v>
+        <v>57384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3315,34 +3319,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577696</v>
+        <v>577851</v>
       </c>
       <c r="R24" t="n">
-        <v>7047755</v>
+        <v>7047625</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3374,7 +3383,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3384,7 +3393,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3411,10 +3425,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122568144</v>
+        <v>122566730</v>
       </c>
       <c r="B25" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3456,10 +3470,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577721</v>
+        <v>577749</v>
       </c>
       <c r="R25" t="n">
-        <v>7047806</v>
+        <v>7047671</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3505,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,7 +3515,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3533,10 +3547,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566730</v>
+        <v>122568941</v>
       </c>
       <c r="B26" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3578,10 +3592,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577749</v>
+        <v>577874</v>
       </c>
       <c r="R26" t="n">
-        <v>7047671</v>
+        <v>7047636</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3613,7 +3627,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3623,12 +3637,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3643,22 +3657,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122568670</v>
+        <v>122568836</v>
       </c>
       <c r="B27" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3671,39 +3685,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577765</v>
+        <v>577845</v>
       </c>
       <c r="R27" t="n">
-        <v>7047696</v>
+        <v>7047652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3735,7 +3744,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3745,12 +3754,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,22 +3769,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566495</v>
+        <v>122566694</v>
       </c>
       <c r="B28" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3822,13 +3826,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577898</v>
+        <v>577770</v>
       </c>
       <c r="R28" t="n">
-        <v>7047638</v>
+        <v>7047663</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3857,7 +3861,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3867,7 +3871,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3887,22 +3891,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566515</v>
+        <v>122566696</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3935,7 +3939,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3944,10 +3948,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577857</v>
+        <v>577752</v>
       </c>
       <c r="R29" t="n">
-        <v>7047693</v>
+        <v>7047671</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,7 +3983,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3989,12 +3993,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4009,22 +4013,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122568120</v>
+        <v>122567250</v>
       </c>
       <c r="B30" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4057,7 +4061,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4066,10 +4070,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577697</v>
+        <v>577683</v>
       </c>
       <c r="R30" t="n">
-        <v>7047768</v>
+        <v>7047626</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4101,7 +4105,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4111,12 +4115,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på två tallar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4143,10 +4147,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567600</v>
+        <v>122568098</v>
       </c>
       <c r="B31" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4188,10 +4192,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577658</v>
+        <v>577684</v>
       </c>
       <c r="R31" t="n">
-        <v>7047696</v>
+        <v>7047782</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4223,7 +4227,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4233,7 +4237,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4253,22 +4257,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567250</v>
+        <v>122566495</v>
       </c>
       <c r="B32" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4301,7 +4305,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4310,13 +4314,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577683</v>
+        <v>577898</v>
       </c>
       <c r="R32" t="n">
-        <v>7047626</v>
+        <v>7047638</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4345,7 +4349,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4355,7 +4359,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4375,22 +4379,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566271</v>
+        <v>122567965</v>
       </c>
       <c r="B33" t="n">
-        <v>57536</v>
+        <v>90834</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4403,42 +4407,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577901</v>
+        <v>577621</v>
       </c>
       <c r="R33" t="n">
-        <v>7047671</v>
+        <v>7047786</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4467,7 +4466,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4477,7 +4476,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4492,22 +4491,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567426</v>
+        <v>122565992</v>
       </c>
       <c r="B34" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4537,26 +4536,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577666</v>
+        <v>577930</v>
       </c>
       <c r="R34" t="n">
-        <v>7047652</v>
+        <v>7047678</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4588,7 +4578,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4598,7 +4588,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4625,10 +4615,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567649</v>
+        <v>122567415</v>
       </c>
       <c r="B35" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4661,7 +4651,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4670,10 +4660,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577631</v>
+        <v>577665</v>
       </c>
       <c r="R35" t="n">
-        <v>7047709</v>
+        <v>7047625</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4705,7 +4695,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4715,12 +4705,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4747,10 +4737,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122568871</v>
+        <v>122566643</v>
       </c>
       <c r="B36" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4763,39 +4753,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577847</v>
+        <v>577816</v>
       </c>
       <c r="R36" t="n">
-        <v>7047657</v>
+        <v>7047681</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4827,7 +4812,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4837,12 +4822,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4857,22 +4837,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567764</v>
+        <v>122568052</v>
       </c>
       <c r="B37" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4885,42 +4865,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577641</v>
+        <v>577647</v>
       </c>
       <c r="R37" t="n">
-        <v>7047789</v>
+        <v>7047774</v>
       </c>
       <c r="S37" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4949,7 +4924,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4959,7 +4934,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4986,10 +4961,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566643</v>
+        <v>122567603</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5002,34 +4977,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577816</v>
+        <v>577640</v>
       </c>
       <c r="R38" t="n">
-        <v>7047681</v>
+        <v>7047712</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5061,7 +5041,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5071,7 +5051,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5098,10 +5083,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122568098</v>
+        <v>122566515</v>
       </c>
       <c r="B39" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5143,10 +5128,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577684</v>
+        <v>577857</v>
       </c>
       <c r="R39" t="n">
-        <v>7047782</v>
+        <v>7047693</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5178,7 +5163,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5188,12 +5173,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5208,22 +5193,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122565992</v>
+        <v>122567600</v>
       </c>
       <c r="B40" t="n">
-        <v>90851</v>
+        <v>57384</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5236,34 +5221,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577930</v>
+        <v>577658</v>
       </c>
       <c r="R40" t="n">
-        <v>7047678</v>
+        <v>7047696</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5295,7 +5285,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5305,7 +5295,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5332,10 +5327,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122568123</v>
+        <v>122566271</v>
       </c>
       <c r="B41" t="n">
-        <v>57383</v>
+        <v>57537</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5348,27 +5343,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5377,13 +5372,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577688</v>
+        <v>577901</v>
       </c>
       <c r="R41" t="n">
-        <v>7047768</v>
+        <v>7047671</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5412,7 +5407,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5422,12 +5417,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,22 +5432,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566696</v>
+        <v>122567761</v>
       </c>
       <c r="B42" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5490,7 +5480,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5499,10 +5489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577752</v>
+        <v>577630</v>
       </c>
       <c r="R42" t="n">
-        <v>7047671</v>
+        <v>7047750</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5534,7 +5524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5544,12 +5534,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5564,22 +5554,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122568836</v>
+        <v>122568123</v>
       </c>
       <c r="B43" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5592,34 +5582,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577845</v>
+        <v>577688</v>
       </c>
       <c r="R43" t="n">
-        <v>7047652</v>
+        <v>7047768</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5651,7 +5646,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5661,7 +5656,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5676,12 +5676,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -1519,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566471</v>
+        <v>122568145</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>90834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,39 +1535,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577878</v>
+        <v>577696</v>
       </c>
       <c r="R9" t="n">
-        <v>7047667</v>
+        <v>7047755</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,12 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122568145</v>
+        <v>122567115</v>
       </c>
       <c r="B10" t="n">
-        <v>90834</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1657,21 +1647,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1681,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577696</v>
+        <v>577719</v>
       </c>
       <c r="R10" t="n">
-        <v>7047755</v>
+        <v>7047669</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,7 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,22 +1731,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567115</v>
+        <v>122566471</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,34 +1759,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577719</v>
+        <v>577878</v>
       </c>
       <c r="R11" t="n">
-        <v>7047669</v>
+        <v>7047667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,7 +1833,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,12 +1853,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567415</v>
+        <v>122566643</v>
       </c>
       <c r="B35" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4631,39 +4631,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577665</v>
+        <v>577816</v>
       </c>
       <c r="R35" t="n">
-        <v>7047625</v>
+        <v>7047681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4695,7 +4690,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4705,12 +4700,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4737,10 +4727,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566643</v>
+        <v>122568052</v>
       </c>
       <c r="B36" t="n">
-        <v>78657</v>
+        <v>79738</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4753,21 +4743,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4777,10 +4767,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577816</v>
+        <v>577647</v>
       </c>
       <c r="R36" t="n">
-        <v>7047681</v>
+        <v>7047774</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4812,7 +4802,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4822,7 +4812,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4837,22 +4827,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122568052</v>
+        <v>122567415</v>
       </c>
       <c r="B37" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4865,34 +4855,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577647</v>
+        <v>577665</v>
       </c>
       <c r="R37" t="n">
-        <v>7047774</v>
+        <v>7047625</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4924,7 +4919,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4934,7 +4929,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4949,12 +4949,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122568670</v>
+        <v>122566471</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577765</v>
+        <v>577878</v>
       </c>
       <c r="R2" t="n">
-        <v>7047696</v>
+        <v>7047667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122568922</v>
+        <v>122568144</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577858</v>
+        <v>577721</v>
       </c>
       <c r="R3" t="n">
-        <v>7047635</v>
+        <v>7047806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,19 +907,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122568871</v>
+        <v>122567649</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577847</v>
+        <v>577631</v>
       </c>
       <c r="R4" t="n">
-        <v>7047657</v>
+        <v>7047709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,19 +1029,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567519</v>
+        <v>122568123</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577659</v>
+        <v>577688</v>
       </c>
       <c r="R5" t="n">
-        <v>7047666</v>
+        <v>7047768</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1151,19 +1151,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122568234</v>
+        <v>122568196</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577772</v>
+        <v>577717</v>
       </c>
       <c r="R6" t="n">
-        <v>7047747</v>
+        <v>7047745</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1273,19 +1273,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567856</v>
+        <v>122568906</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577598</v>
+        <v>577851</v>
       </c>
       <c r="R7" t="n">
-        <v>7047750</v>
+        <v>7047625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,12 +1375,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,22 +1395,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567286</v>
+        <v>122566694</v>
       </c>
       <c r="B8" t="n">
-        <v>90834</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1423,34 +1423,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577696</v>
+        <v>577770</v>
       </c>
       <c r="R8" t="n">
-        <v>7047629</v>
+        <v>7047663</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1497,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,22 +1517,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122568145</v>
+        <v>122568234</v>
       </c>
       <c r="B9" t="n">
-        <v>90834</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,34 +1545,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577696</v>
+        <v>577772</v>
       </c>
       <c r="R9" t="n">
-        <v>7047755</v>
+        <v>7047747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1619,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,22 +1639,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567115</v>
+        <v>122568871</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,34 +1667,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577719</v>
+        <v>577847</v>
       </c>
       <c r="R10" t="n">
-        <v>7047669</v>
+        <v>7047657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1741,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,19 +1761,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566471</v>
+        <v>122566730</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1788,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577878</v>
+        <v>577749</v>
       </c>
       <c r="R11" t="n">
-        <v>7047667</v>
+        <v>7047671</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,12 +1863,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,22 +1883,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122568144</v>
+        <v>122566643</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1881,39 +1911,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577721</v>
+        <v>577816</v>
       </c>
       <c r="R12" t="n">
-        <v>7047806</v>
+        <v>7047681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,7 +1970,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,12 +1980,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,7 +2007,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567504</v>
+        <v>122567250</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -2023,7 +2043,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2032,10 +2052,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577648</v>
+        <v>577683</v>
       </c>
       <c r="R13" t="n">
-        <v>7047682</v>
+        <v>7047626</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2077,7 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2097,19 +2117,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567649</v>
+        <v>122567600</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -2154,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577631</v>
+        <v>577658</v>
       </c>
       <c r="R14" t="n">
-        <v>7047709</v>
+        <v>7047696</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,7 +2209,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2199,7 +2219,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2219,22 +2239,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122568013</v>
+        <v>122566494</v>
       </c>
       <c r="B15" t="n">
-        <v>90834</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,34 +2267,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577636</v>
+        <v>577868</v>
       </c>
       <c r="R15" t="n">
-        <v>7047783</v>
+        <v>7047668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2306,7 +2331,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2316,7 +2341,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2343,10 +2373,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566508</v>
+        <v>122567761</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2359,34 +2389,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577875</v>
+        <v>577630</v>
       </c>
       <c r="R16" t="n">
-        <v>7047661</v>
+        <v>7047750</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2418,7 +2453,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2428,7 +2463,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,19 +2483,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566768</v>
+        <v>122568098</v>
       </c>
       <c r="B17" t="n">
         <v>57384</v>
@@ -2491,7 +2531,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2500,10 +2540,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577712</v>
+        <v>577684</v>
       </c>
       <c r="R17" t="n">
-        <v>7047643</v>
+        <v>7047782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2535,7 +2575,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2545,12 +2585,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,22 +2605,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567426</v>
+        <v>122565992</v>
       </c>
       <c r="B18" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2610,26 +2650,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577666</v>
+        <v>577930</v>
       </c>
       <c r="R18" t="n">
-        <v>7047652</v>
+        <v>7047678</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2661,7 +2692,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2671,7 +2702,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2698,7 +2729,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122568120</v>
+        <v>122567603</v>
       </c>
       <c r="B19" t="n">
         <v>57384</v>
@@ -2743,10 +2774,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577697</v>
+        <v>577640</v>
       </c>
       <c r="R19" t="n">
-        <v>7047768</v>
+        <v>7047712</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2778,7 +2809,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2788,12 +2819,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på två tallar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2808,19 +2839,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567764</v>
+        <v>122567415</v>
       </c>
       <c r="B20" t="n">
         <v>57384</v>
@@ -2856,7 +2887,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2865,13 +2896,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577641</v>
+        <v>577665</v>
       </c>
       <c r="R20" t="n">
-        <v>7047789</v>
+        <v>7047625</v>
       </c>
       <c r="S20" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2900,7 +2931,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2910,7 +2941,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,22 +2961,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568196</v>
+        <v>122568145</v>
       </c>
       <c r="B21" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2953,39 +2989,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577717</v>
+        <v>577696</v>
       </c>
       <c r="R21" t="n">
-        <v>7047745</v>
+        <v>7047755</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3017,7 +3048,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,12 +3058,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3059,10 +3085,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566485</v>
+        <v>122567115</v>
       </c>
       <c r="B22" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3075,39 +3101,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577908</v>
+        <v>577719</v>
       </c>
       <c r="R22" t="n">
-        <v>7047646</v>
+        <v>7047669</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3139,7 +3160,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3149,12 +3170,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3181,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566494</v>
+        <v>122568052</v>
       </c>
       <c r="B23" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3197,39 +3213,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577868</v>
+        <v>577647</v>
       </c>
       <c r="R23" t="n">
-        <v>7047668</v>
+        <v>7047774</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3261,7 +3272,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3271,12 +3282,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3303,10 +3309,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122568906</v>
+        <v>122568836</v>
       </c>
       <c r="B24" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3319,39 +3325,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577851</v>
+        <v>577845</v>
       </c>
       <c r="R24" t="n">
-        <v>7047625</v>
+        <v>7047652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3383,7 +3384,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3393,12 +3394,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3413,19 +3409,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566730</v>
+        <v>122568922</v>
       </c>
       <c r="B25" t="n">
         <v>57384</v>
@@ -3470,10 +3466,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577749</v>
+        <v>577858</v>
       </c>
       <c r="R25" t="n">
-        <v>7047671</v>
+        <v>7047635</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3505,7 +3501,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3515,12 +3511,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3535,19 +3531,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122568941</v>
+        <v>122566495</v>
       </c>
       <c r="B26" t="n">
         <v>57384</v>
@@ -3592,13 +3588,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577874</v>
+        <v>577898</v>
       </c>
       <c r="R26" t="n">
-        <v>7047636</v>
+        <v>7047638</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3627,7 +3623,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3637,12 +3633,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3657,22 +3653,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122568836</v>
+        <v>122566508</v>
       </c>
       <c r="B27" t="n">
-        <v>79738</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3685,21 +3681,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3709,10 +3705,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577845</v>
+        <v>577875</v>
       </c>
       <c r="R27" t="n">
-        <v>7047652</v>
+        <v>7047661</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3744,7 +3740,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3754,7 +3750,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3769,22 +3765,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566694</v>
+        <v>122566271</v>
       </c>
       <c r="B28" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3797,27 +3793,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3826,13 +3822,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577770</v>
+        <v>577901</v>
       </c>
       <c r="R28" t="n">
-        <v>7047663</v>
+        <v>7047671</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3861,7 +3857,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3871,12 +3867,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3903,10 +3894,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566696</v>
+        <v>122567965</v>
       </c>
       <c r="B29" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3919,39 +3910,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577752</v>
+        <v>577621</v>
       </c>
       <c r="R29" t="n">
-        <v>7047671</v>
+        <v>7047786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3983,7 +3969,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3993,12 +3979,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4025,10 +4006,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567250</v>
+        <v>122568013</v>
       </c>
       <c r="B30" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4041,39 +4022,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577683</v>
+        <v>577636</v>
       </c>
       <c r="R30" t="n">
-        <v>7047626</v>
+        <v>7047783</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4105,7 +4081,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4115,12 +4091,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4147,7 +4118,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122568098</v>
+        <v>122568670</v>
       </c>
       <c r="B31" t="n">
         <v>57384</v>
@@ -4192,10 +4163,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577684</v>
+        <v>577765</v>
       </c>
       <c r="R31" t="n">
-        <v>7047782</v>
+        <v>7047696</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4227,7 +4198,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4237,7 +4208,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4257,19 +4228,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566495</v>
+        <v>122567504</v>
       </c>
       <c r="B32" t="n">
         <v>57384</v>
@@ -4314,13 +4285,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577898</v>
+        <v>577648</v>
       </c>
       <c r="R32" t="n">
-        <v>7047638</v>
+        <v>7047682</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4349,7 +4320,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4359,7 +4330,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4391,10 +4362,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567965</v>
+        <v>122566515</v>
       </c>
       <c r="B33" t="n">
-        <v>90834</v>
+        <v>57384</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4407,34 +4378,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577621</v>
+        <v>577857</v>
       </c>
       <c r="R33" t="n">
-        <v>7047786</v>
+        <v>7047693</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4466,7 +4442,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4476,7 +4452,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4491,22 +4472,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122565992</v>
+        <v>122566696</v>
       </c>
       <c r="B34" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4519,34 +4500,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577930</v>
+        <v>577752</v>
       </c>
       <c r="R34" t="n">
-        <v>7047678</v>
+        <v>7047671</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4578,7 +4564,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4588,7 +4574,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4603,22 +4594,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566643</v>
+        <v>122567856</v>
       </c>
       <c r="B35" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4631,34 +4622,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577816</v>
+        <v>577598</v>
       </c>
       <c r="R35" t="n">
-        <v>7047681</v>
+        <v>7047750</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4690,7 +4686,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4700,7 +4696,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4727,10 +4728,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122568052</v>
+        <v>122568941</v>
       </c>
       <c r="B36" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4743,34 +4744,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577647</v>
+        <v>577874</v>
       </c>
       <c r="R36" t="n">
-        <v>7047774</v>
+        <v>7047636</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4802,7 +4808,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4812,7 +4818,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4839,7 +4850,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567415</v>
+        <v>122566768</v>
       </c>
       <c r="B37" t="n">
         <v>57384</v>
@@ -4884,10 +4895,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577665</v>
+        <v>577712</v>
       </c>
       <c r="R37" t="n">
-        <v>7047625</v>
+        <v>7047643</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4919,7 +4930,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4929,7 +4940,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4949,19 +4960,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567603</v>
+        <v>122567764</v>
       </c>
       <c r="B38" t="n">
         <v>57384</v>
@@ -4997,7 +5008,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5006,13 +5017,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577640</v>
+        <v>577641</v>
       </c>
       <c r="R38" t="n">
-        <v>7047712</v>
+        <v>7047789</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5041,7 +5052,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5051,12 +5062,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5071,19 +5077,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566515</v>
+        <v>122567519</v>
       </c>
       <c r="B39" t="n">
         <v>57384</v>
@@ -5128,10 +5134,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577857</v>
+        <v>577659</v>
       </c>
       <c r="R39" t="n">
-        <v>7047693</v>
+        <v>7047666</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5163,7 +5169,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5173,12 +5179,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5193,22 +5199,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567600</v>
+        <v>122567426</v>
       </c>
       <c r="B40" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5221,27 +5227,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5250,10 +5260,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577658</v>
+        <v>577666</v>
       </c>
       <c r="R40" t="n">
-        <v>7047696</v>
+        <v>7047652</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5285,7 +5295,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5295,12 +5305,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5327,10 +5332,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566271</v>
+        <v>122567286</v>
       </c>
       <c r="B41" t="n">
-        <v>57537</v>
+        <v>90837</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5343,42 +5348,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577901</v>
+        <v>577696</v>
       </c>
       <c r="R41" t="n">
-        <v>7047671</v>
+        <v>7047629</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5432,19 +5432,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567761</v>
+        <v>122568120</v>
       </c>
       <c r="B42" t="n">
         <v>57384</v>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577630</v>
+        <v>577697</v>
       </c>
       <c r="R42" t="n">
-        <v>7047750</v>
+        <v>7047768</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5554,19 +5554,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122568123</v>
+        <v>122566485</v>
       </c>
       <c r="B43" t="n">
         <v>57384</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577688</v>
+        <v>577908</v>
       </c>
       <c r="R43" t="n">
-        <v>7047768</v>
+        <v>7047646</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566471</v>
+        <v>122568013</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577878</v>
+        <v>577636</v>
       </c>
       <c r="R2" t="n">
-        <v>7047667</v>
+        <v>7047783</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122568144</v>
+        <v>122568196</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577721</v>
+        <v>577717</v>
       </c>
       <c r="R3" t="n">
-        <v>7047806</v>
+        <v>7047745</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567649</v>
+        <v>122566271</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,27 +925,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577631</v>
+        <v>577901</v>
       </c>
       <c r="R4" t="n">
-        <v>7047709</v>
+        <v>7047671</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122568123</v>
+        <v>122566508</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577688</v>
+        <v>577875</v>
       </c>
       <c r="R5" t="n">
-        <v>7047768</v>
+        <v>7047661</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122568196</v>
+        <v>122567426</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,27 +1154,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577717</v>
+        <v>577666</v>
       </c>
       <c r="R6" t="n">
-        <v>7047745</v>
+        <v>7047652</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122568906</v>
+        <v>122566768</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1321,7 +1295,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1330,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577851</v>
+        <v>577712</v>
       </c>
       <c r="R7" t="n">
-        <v>7047625</v>
+        <v>7047643</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1407,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566694</v>
+        <v>122567504</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1452,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577770</v>
+        <v>577648</v>
       </c>
       <c r="R8" t="n">
-        <v>7047663</v>
+        <v>7047682</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1517,22 +1491,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122568234</v>
+        <v>122568145</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,39 +1519,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577772</v>
+        <v>577696</v>
       </c>
       <c r="R9" t="n">
-        <v>7047747</v>
+        <v>7047755</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1619,12 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,22 +1603,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122568871</v>
+        <v>122567286</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,39 +1631,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577847</v>
+        <v>577696</v>
       </c>
       <c r="R10" t="n">
-        <v>7047657</v>
+        <v>7047629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1741,12 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,19 +1715,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566730</v>
+        <v>122567761</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1818,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577749</v>
+        <v>577630</v>
       </c>
       <c r="R11" t="n">
-        <v>7047671</v>
+        <v>7047750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,12 +1817,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,22 +1837,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566643</v>
+        <v>122567603</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,34 +1865,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577816</v>
+        <v>577640</v>
       </c>
       <c r="R12" t="n">
-        <v>7047681</v>
+        <v>7047712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1980,7 +1939,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2007,7 +1971,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567250</v>
+        <v>122568234</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -2043,7 +2007,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2052,10 +2016,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577683</v>
+        <v>577772</v>
       </c>
       <c r="R13" t="n">
-        <v>7047626</v>
+        <v>7047747</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,7 +2051,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2061,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2117,19 +2081,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567600</v>
+        <v>122566494</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -2174,10 +2138,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577658</v>
+        <v>577868</v>
       </c>
       <c r="R14" t="n">
-        <v>7047696</v>
+        <v>7047668</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2209,7 +2173,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2219,12 +2183,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,7 +2215,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566494</v>
+        <v>122566495</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2296,13 +2260,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577868</v>
+        <v>577898</v>
       </c>
       <c r="R15" t="n">
-        <v>7047668</v>
+        <v>7047638</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2331,7 +2295,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2341,12 +2305,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2361,19 +2325,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567761</v>
+        <v>122568098</v>
       </c>
       <c r="B16" t="n">
         <v>57384</v>
@@ -2418,10 +2382,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577630</v>
+        <v>577684</v>
       </c>
       <c r="R16" t="n">
-        <v>7047750</v>
+        <v>7047782</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2453,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2463,12 +2427,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2483,19 +2447,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122568098</v>
+        <v>122568906</v>
       </c>
       <c r="B17" t="n">
         <v>57384</v>
@@ -2540,10 +2504,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577684</v>
+        <v>577851</v>
       </c>
       <c r="R17" t="n">
-        <v>7047782</v>
+        <v>7047625</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2575,7 +2539,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2585,12 +2549,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2605,22 +2569,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122565992</v>
+        <v>122568052</v>
       </c>
       <c r="B18" t="n">
-        <v>90855</v>
+        <v>79741</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2633,21 +2597,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2657,10 +2621,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577930</v>
+        <v>577647</v>
       </c>
       <c r="R18" t="n">
-        <v>7047678</v>
+        <v>7047774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2692,7 +2656,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2702,7 +2666,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2729,10 +2693,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567603</v>
+        <v>122568836</v>
       </c>
       <c r="B19" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2745,39 +2709,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577640</v>
+        <v>577845</v>
       </c>
       <c r="R19" t="n">
-        <v>7047712</v>
+        <v>7047652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2809,7 +2768,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2819,12 +2778,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2839,19 +2793,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567415</v>
+        <v>122566471</v>
       </c>
       <c r="B20" t="n">
         <v>57384</v>
@@ -2887,7 +2841,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2896,10 +2850,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577665</v>
+        <v>577878</v>
       </c>
       <c r="R20" t="n">
-        <v>7047625</v>
+        <v>7047667</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2931,7 +2885,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2941,7 +2895,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2961,22 +2915,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568145</v>
+        <v>122567600</v>
       </c>
       <c r="B21" t="n">
-        <v>90837</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2989,34 +2943,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577696</v>
+        <v>577658</v>
       </c>
       <c r="R21" t="n">
-        <v>7047755</v>
+        <v>7047696</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3048,7 +3007,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3058,7 +3017,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567115</v>
+        <v>122567965</v>
       </c>
       <c r="B22" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3101,21 +3065,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3125,10 +3089,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577719</v>
+        <v>577621</v>
       </c>
       <c r="R22" t="n">
-        <v>7047669</v>
+        <v>7047786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3160,7 +3124,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3170,7 +3134,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3197,10 +3161,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122568052</v>
+        <v>122567115</v>
       </c>
       <c r="B23" t="n">
-        <v>79741</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3213,21 +3177,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3237,10 +3201,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577647</v>
+        <v>577719</v>
       </c>
       <c r="R23" t="n">
-        <v>7047774</v>
+        <v>7047669</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3272,7 +3236,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3282,7 +3246,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3297,22 +3261,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122568836</v>
+        <v>122566694</v>
       </c>
       <c r="B24" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3325,34 +3289,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577845</v>
+        <v>577770</v>
       </c>
       <c r="R24" t="n">
-        <v>7047652</v>
+        <v>7047663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3384,7 +3353,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3394,7 +3363,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3409,19 +3383,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122568922</v>
+        <v>122566730</v>
       </c>
       <c r="B25" t="n">
         <v>57384</v>
@@ -3466,10 +3440,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577858</v>
+        <v>577749</v>
       </c>
       <c r="R25" t="n">
-        <v>7047635</v>
+        <v>7047671</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3501,7 +3475,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3511,12 +3485,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3531,19 +3505,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566495</v>
+        <v>122568670</v>
       </c>
       <c r="B26" t="n">
         <v>57384</v>
@@ -3588,13 +3562,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577898</v>
+        <v>577765</v>
       </c>
       <c r="R26" t="n">
-        <v>7047638</v>
+        <v>7047696</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3623,7 +3597,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3633,7 +3607,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3653,19 +3627,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566508</v>
+        <v>122566643</v>
       </c>
       <c r="B27" t="n">
         <v>78660</v>
@@ -3705,10 +3679,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577875</v>
+        <v>577816</v>
       </c>
       <c r="R27" t="n">
-        <v>7047661</v>
+        <v>7047681</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3740,7 +3714,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3750,7 +3724,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3777,10 +3751,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566271</v>
+        <v>122567764</v>
       </c>
       <c r="B28" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3793,27 +3767,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3822,13 +3796,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577901</v>
+        <v>577641</v>
       </c>
       <c r="R28" t="n">
-        <v>7047671</v>
+        <v>7047789</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3857,7 +3831,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3867,7 +3841,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3894,10 +3868,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567965</v>
+        <v>122567649</v>
       </c>
       <c r="B29" t="n">
-        <v>90837</v>
+        <v>57384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3910,34 +3884,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577621</v>
+        <v>577631</v>
       </c>
       <c r="R29" t="n">
-        <v>7047786</v>
+        <v>7047709</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3969,7 +3948,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3979,7 +3958,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4006,10 +3990,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122568013</v>
+        <v>122568871</v>
       </c>
       <c r="B30" t="n">
-        <v>90837</v>
+        <v>57384</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4022,34 +4006,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577636</v>
+        <v>577847</v>
       </c>
       <c r="R30" t="n">
-        <v>7047783</v>
+        <v>7047657</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4081,7 +4070,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4091,7 +4080,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4118,7 +4112,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122568670</v>
+        <v>122567250</v>
       </c>
       <c r="B31" t="n">
         <v>57384</v>
@@ -4154,7 +4148,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4163,10 +4157,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577765</v>
+        <v>577683</v>
       </c>
       <c r="R31" t="n">
-        <v>7047696</v>
+        <v>7047626</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4198,7 +4192,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4208,7 +4202,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4240,7 +4234,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567504</v>
+        <v>122567519</v>
       </c>
       <c r="B32" t="n">
         <v>57384</v>
@@ -4285,10 +4279,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577648</v>
+        <v>577659</v>
       </c>
       <c r="R32" t="n">
-        <v>7047682</v>
+        <v>7047666</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4320,7 +4314,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4330,7 +4324,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4350,22 +4344,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566515</v>
+        <v>122565992</v>
       </c>
       <c r="B33" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4378,39 +4372,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577857</v>
+        <v>577930</v>
       </c>
       <c r="R33" t="n">
-        <v>7047693</v>
+        <v>7047678</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4442,7 +4431,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4452,12 +4441,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4472,19 +4456,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566696</v>
+        <v>122568120</v>
       </c>
       <c r="B34" t="n">
         <v>57384</v>
@@ -4520,7 +4504,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4529,10 +4513,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577752</v>
+        <v>577697</v>
       </c>
       <c r="R34" t="n">
-        <v>7047671</v>
+        <v>7047768</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4564,7 +4548,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4574,12 +4558,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4594,12 +4578,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4850,7 +4834,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566768</v>
+        <v>122566485</v>
       </c>
       <c r="B37" t="n">
         <v>57384</v>
@@ -4886,7 +4870,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4895,10 +4879,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577712</v>
+        <v>577908</v>
       </c>
       <c r="R37" t="n">
-        <v>7047643</v>
+        <v>7047646</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4930,7 +4914,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4940,7 +4924,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4960,19 +4944,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567764</v>
+        <v>122566696</v>
       </c>
       <c r="B38" t="n">
         <v>57384</v>
@@ -5008,7 +4992,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5017,13 +5001,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577641</v>
+        <v>577752</v>
       </c>
       <c r="R38" t="n">
-        <v>7047789</v>
+        <v>7047671</v>
       </c>
       <c r="S38" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5052,7 +5036,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5062,7 +5046,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5077,19 +5066,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567519</v>
+        <v>122568922</v>
       </c>
       <c r="B39" t="n">
         <v>57384</v>
@@ -5134,10 +5123,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577659</v>
+        <v>577858</v>
       </c>
       <c r="R39" t="n">
-        <v>7047666</v>
+        <v>7047635</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5169,7 +5158,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5179,12 +5168,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5199,22 +5188,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567426</v>
+        <v>122568144</v>
       </c>
       <c r="B40" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5227,31 +5216,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5260,10 +5245,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577666</v>
+        <v>577721</v>
       </c>
       <c r="R40" t="n">
-        <v>7047652</v>
+        <v>7047806</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5295,7 +5280,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5305,7 +5290,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5320,22 +5310,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567286</v>
+        <v>122567415</v>
       </c>
       <c r="B41" t="n">
-        <v>90837</v>
+        <v>57384</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5348,34 +5338,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577696</v>
+        <v>577665</v>
       </c>
       <c r="R41" t="n">
-        <v>7047629</v>
+        <v>7047625</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5407,7 +5402,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5417,7 +5412,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5444,7 +5444,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122568120</v>
+        <v>122566515</v>
       </c>
       <c r="B42" t="n">
         <v>57384</v>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577697</v>
+        <v>577857</v>
       </c>
       <c r="R42" t="n">
-        <v>7047768</v>
+        <v>7047693</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på två tallar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5554,19 +5554,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566485</v>
+        <v>122568123</v>
       </c>
       <c r="B43" t="n">
         <v>57384</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577908</v>
+        <v>577688</v>
       </c>
       <c r="R43" t="n">
-        <v>7047646</v>
+        <v>7047768</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -1615,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567286</v>
+        <v>122567761</v>
       </c>
       <c r="B10" t="n">
-        <v>90837</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,34 +1631,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577696</v>
+        <v>577630</v>
       </c>
       <c r="R10" t="n">
-        <v>7047629</v>
+        <v>7047750</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1705,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,22 +1725,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567761</v>
+        <v>122567286</v>
       </c>
       <c r="B11" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,39 +1753,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577630</v>
+        <v>577696</v>
       </c>
       <c r="R11" t="n">
-        <v>7047750</v>
+        <v>7047629</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,12 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,12 +1837,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122568670</v>
+        <v>122566643</v>
       </c>
       <c r="B26" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3533,39 +3533,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577765</v>
+        <v>577816</v>
       </c>
       <c r="R26" t="n">
-        <v>7047696</v>
+        <v>7047681</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,7 +3592,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3607,12 +3602,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3627,22 +3617,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566643</v>
+        <v>122568670</v>
       </c>
       <c r="B27" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3655,34 +3645,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577816</v>
+        <v>577765</v>
       </c>
       <c r="R27" t="n">
-        <v>7047681</v>
+        <v>7047696</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3714,7 +3709,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3724,7 +3719,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3739,12 +3739,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -2465,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567286</v>
+        <v>122568196</v>
       </c>
       <c r="B17" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,34 +2481,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577696</v>
+        <v>577717</v>
       </c>
       <c r="R17" t="n">
-        <v>7047629</v>
+        <v>7047745</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,7 +2545,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,7 +2555,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,22 +2575,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122568196</v>
+        <v>122567286</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2593,39 +2603,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577717</v>
+        <v>577696</v>
       </c>
       <c r="R18" t="n">
-        <v>7047745</v>
+        <v>7047629</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2667,12 +2672,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2687,12 +2687,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -2465,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122568196</v>
+        <v>122567286</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,39 +2481,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577717</v>
+        <v>577696</v>
       </c>
       <c r="R17" t="n">
-        <v>7047745</v>
+        <v>7047629</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2545,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2555,12 +2550,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2575,22 +2565,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567286</v>
+        <v>122568196</v>
       </c>
       <c r="B18" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2603,34 +2593,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577696</v>
+        <v>577717</v>
       </c>
       <c r="R18" t="n">
-        <v>7047629</v>
+        <v>7047745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2657,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,7 +2667,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2687,12 +2687,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567426</v>
+        <v>122568836</v>
       </c>
       <c r="B26" t="n">
-        <v>90958</v>
+        <v>79843</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3549,40 +3549,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577666</v>
+        <v>577845</v>
       </c>
       <c r="R26" t="n">
         <v>7047652</v>
@@ -3617,7 +3608,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3627,7 +3618,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,12 +3633,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3776,10 +3767,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122568836</v>
+        <v>122567764</v>
       </c>
       <c r="B28" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3792,37 +3783,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577845</v>
+        <v>577641</v>
       </c>
       <c r="R28" t="n">
-        <v>7047652</v>
+        <v>7047789</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3851,7 +3847,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3861,7 +3857,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3876,22 +3872,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567764</v>
+        <v>122567426</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>90958</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3904,27 +3900,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3933,13 +3933,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577641</v>
+        <v>577666</v>
       </c>
       <c r="R29" t="n">
-        <v>7047789</v>
+        <v>7047652</v>
       </c>
       <c r="S29" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567965</v>
+        <v>122566694</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577621</v>
+        <v>577770</v>
       </c>
       <c r="R2" t="n">
-        <v>7047786</v>
+        <v>7047663</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122568871</v>
+        <v>122567965</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577847</v>
+        <v>577621</v>
       </c>
       <c r="R3" t="n">
-        <v>7047657</v>
+        <v>7047786</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122568145</v>
+        <v>122566271</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +925,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577696</v>
+        <v>577901</v>
       </c>
       <c r="R4" t="n">
-        <v>7047755</v>
+        <v>7047671</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122568013</v>
+        <v>122567603</v>
       </c>
       <c r="B5" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577636</v>
+        <v>577640</v>
       </c>
       <c r="R5" t="n">
-        <v>7047783</v>
+        <v>7047712</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,19 +1136,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122568144</v>
+        <v>122568871</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1178,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577721</v>
+        <v>577847</v>
       </c>
       <c r="R6" t="n">
-        <v>7047806</v>
+        <v>7047657</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1238,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1258,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566494</v>
+        <v>122566643</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577868</v>
+        <v>577816</v>
       </c>
       <c r="R7" t="n">
-        <v>7047668</v>
+        <v>7047681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,19 +1370,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566768</v>
+        <v>122568670</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1413,7 +1418,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577712</v>
+        <v>577765</v>
       </c>
       <c r="R8" t="n">
-        <v>7047643</v>
+        <v>7047696</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,12 +1472,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122568670</v>
+        <v>122568196</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1544,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577765</v>
+        <v>577717</v>
       </c>
       <c r="R9" t="n">
-        <v>7047696</v>
+        <v>7047745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1621,7 +1626,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122568123</v>
+        <v>122567764</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1657,7 +1662,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1666,13 +1671,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577688</v>
+        <v>577641</v>
       </c>
       <c r="R10" t="n">
-        <v>7047768</v>
+        <v>7047789</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,12 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,19 +1731,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567603</v>
+        <v>122568906</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577640</v>
+        <v>577851</v>
       </c>
       <c r="R11" t="n">
-        <v>7047712</v>
+        <v>7047625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,19 +1853,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566730</v>
+        <v>122567250</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1901,7 +1901,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577749</v>
+        <v>577683</v>
       </c>
       <c r="R12" t="n">
-        <v>7047671</v>
+        <v>7047626</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1975,19 +1975,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122568120</v>
+        <v>122567649</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577697</v>
+        <v>577631</v>
       </c>
       <c r="R13" t="n">
-        <v>7047768</v>
+        <v>7047709</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på två tallar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,19 +2097,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567519</v>
+        <v>122566730</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577659</v>
+        <v>577749</v>
       </c>
       <c r="R14" t="n">
-        <v>7047666</v>
+        <v>7047671</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2219,19 +2219,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567504</v>
+        <v>122567415</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2267,7 +2267,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577648</v>
+        <v>577665</v>
       </c>
       <c r="R15" t="n">
-        <v>7047682</v>
+        <v>7047625</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,10 +2353,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567115</v>
+        <v>122566471</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,34 +2369,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577719</v>
+        <v>577878</v>
       </c>
       <c r="R16" t="n">
-        <v>7047669</v>
+        <v>7047667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2428,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2438,7 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2453,22 +2463,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567286</v>
+        <v>122568013</v>
       </c>
       <c r="B17" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,10 +2515,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577696</v>
+        <v>577636</v>
       </c>
       <c r="R17" t="n">
-        <v>7047629</v>
+        <v>7047783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,7 +2550,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,7 +2560,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,22 +2575,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122568196</v>
+        <v>122568052</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2593,39 +2603,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577717</v>
+        <v>577647</v>
       </c>
       <c r="R18" t="n">
-        <v>7047745</v>
+        <v>7047774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2667,12 +2672,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2699,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122568941</v>
+        <v>122565992</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,39 +2715,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577874</v>
+        <v>577930</v>
       </c>
       <c r="R19" t="n">
-        <v>7047636</v>
+        <v>7047678</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2774,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2784,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2821,7 +2811,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566696</v>
+        <v>122568922</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2857,7 +2847,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2866,10 +2856,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577752</v>
+        <v>577858</v>
       </c>
       <c r="R20" t="n">
-        <v>7047671</v>
+        <v>7047635</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2901,7 +2891,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2911,12 +2901,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2931,22 +2921,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566508</v>
+        <v>122567115</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2983,10 +2973,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577875</v>
+        <v>577719</v>
       </c>
       <c r="R21" t="n">
-        <v>7047661</v>
+        <v>7047669</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3018,7 +3008,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3028,7 +3018,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,10 +3045,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122568052</v>
+        <v>122567761</v>
       </c>
       <c r="B22" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3071,34 +3061,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577647</v>
+        <v>577630</v>
       </c>
       <c r="R22" t="n">
-        <v>7047774</v>
+        <v>7047750</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3140,7 +3135,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3155,19 +3155,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567415</v>
+        <v>122567519</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3203,7 +3203,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577665</v>
+        <v>577659</v>
       </c>
       <c r="R23" t="n">
-        <v>7047625</v>
+        <v>7047666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3277,19 +3277,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566515</v>
+        <v>122566768</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3325,7 +3325,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577857</v>
+        <v>577712</v>
       </c>
       <c r="R24" t="n">
-        <v>7047693</v>
+        <v>7047643</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3399,19 +3399,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566485</v>
+        <v>122568098</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577908</v>
+        <v>577684</v>
       </c>
       <c r="R25" t="n">
-        <v>7047646</v>
+        <v>7047782</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122568836</v>
+        <v>122567856</v>
       </c>
       <c r="B26" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3549,34 +3549,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577845</v>
+        <v>577598</v>
       </c>
       <c r="R26" t="n">
-        <v>7047652</v>
+        <v>7047750</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3608,7 +3613,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3618,7 +3623,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3633,12 +3643,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3767,7 +3777,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567764</v>
+        <v>122568120</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3803,7 +3813,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3812,13 +3822,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577641</v>
+        <v>577697</v>
       </c>
       <c r="R28" t="n">
-        <v>7047789</v>
+        <v>7047768</v>
       </c>
       <c r="S28" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3847,7 +3857,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3857,7 +3867,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3884,10 +3899,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567426</v>
+        <v>122568941</v>
       </c>
       <c r="B29" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3900,31 +3915,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3933,10 +3944,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577666</v>
+        <v>577874</v>
       </c>
       <c r="R29" t="n">
-        <v>7047652</v>
+        <v>7047636</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3968,7 +3979,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3978,7 +3989,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4005,10 +4021,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566471</v>
+        <v>122568836</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4021,39 +4037,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577878</v>
+        <v>577845</v>
       </c>
       <c r="R30" t="n">
-        <v>7047667</v>
+        <v>7047652</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4085,7 +4096,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4095,12 +4106,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4115,19 +4121,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122568922</v>
+        <v>122567600</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4172,10 +4178,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577858</v>
+        <v>577658</v>
       </c>
       <c r="R31" t="n">
-        <v>7047635</v>
+        <v>7047696</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4207,7 +4213,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4217,12 +4223,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4237,19 +4243,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567600</v>
+        <v>122566485</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4294,10 +4300,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577658</v>
+        <v>577908</v>
       </c>
       <c r="R32" t="n">
-        <v>7047696</v>
+        <v>7047646</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4329,7 +4335,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4339,12 +4345,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4359,19 +4365,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122568906</v>
+        <v>122567504</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4416,10 +4422,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577851</v>
+        <v>577648</v>
       </c>
       <c r="R33" t="n">
-        <v>7047625</v>
+        <v>7047682</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4451,7 +4457,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4461,12 +4467,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4481,22 +4487,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566694</v>
+        <v>122566508</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4509,39 +4515,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577770</v>
+        <v>577875</v>
       </c>
       <c r="R34" t="n">
-        <v>7047663</v>
+        <v>7047661</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4573,7 +4574,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4583,12 +4584,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4603,22 +4599,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567649</v>
+        <v>122568145</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4631,39 +4627,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577631</v>
+        <v>577696</v>
       </c>
       <c r="R35" t="n">
-        <v>7047709</v>
+        <v>7047755</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4695,7 +4686,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4705,12 +4696,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4725,19 +4711,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567250</v>
+        <v>122566515</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4773,7 +4759,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4782,10 +4768,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577683</v>
+        <v>577857</v>
       </c>
       <c r="R36" t="n">
-        <v>7047626</v>
+        <v>7047693</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4817,7 +4803,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4827,12 +4813,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4847,22 +4833,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566271</v>
+        <v>122567426</v>
       </c>
       <c r="B37" t="n">
-        <v>57631</v>
+        <v>90962</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4875,27 +4861,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4904,13 +4894,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577901</v>
+        <v>577666</v>
       </c>
       <c r="R37" t="n">
-        <v>7047671</v>
+        <v>7047652</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4939,7 +4929,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4949,7 +4939,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4976,10 +4966,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566643</v>
+        <v>122568144</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4992,34 +4982,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577816</v>
+        <v>577721</v>
       </c>
       <c r="R38" t="n">
-        <v>7047681</v>
+        <v>7047806</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5051,7 +5046,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5061,7 +5056,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5088,7 +5088,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122568098</v>
+        <v>122568123</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577684</v>
+        <v>577688</v>
       </c>
       <c r="R39" t="n">
-        <v>7047782</v>
+        <v>7047768</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5210,7 +5210,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567761</v>
+        <v>122566696</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -5246,7 +5246,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577630</v>
+        <v>577752</v>
       </c>
       <c r="R40" t="n">
-        <v>7047750</v>
+        <v>7047671</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5320,19 +5320,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567856</v>
+        <v>122566494</v>
       </c>
       <c r="B41" t="n">
         <v>57478</v>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577598</v>
+        <v>577868</v>
       </c>
       <c r="R41" t="n">
-        <v>7047750</v>
+        <v>7047668</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,22 +5442,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122568234</v>
+        <v>122567286</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5470,39 +5470,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577772</v>
+        <v>577696</v>
       </c>
       <c r="R42" t="n">
-        <v>7047747</v>
+        <v>7047629</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5534,7 +5529,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5544,12 +5539,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5576,10 +5566,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122565992</v>
+        <v>122568234</v>
       </c>
       <c r="B43" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5592,34 +5582,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577930</v>
+        <v>577772</v>
       </c>
       <c r="R43" t="n">
-        <v>7047678</v>
+        <v>7047747</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5651,7 +5646,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5661,7 +5656,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5676,12 +5676,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566694</v>
+        <v>122567856</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577770</v>
+        <v>577598</v>
       </c>
       <c r="R2" t="n">
-        <v>7047663</v>
+        <v>7047750</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567965</v>
+        <v>122568941</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577621</v>
+        <v>577874</v>
       </c>
       <c r="R3" t="n">
-        <v>7047786</v>
+        <v>7047636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566271</v>
+        <v>122568196</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,27 +935,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577901</v>
+        <v>577717</v>
       </c>
       <c r="R4" t="n">
-        <v>7047671</v>
+        <v>7047745</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567603</v>
+        <v>122568234</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1071,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577640</v>
+        <v>577772</v>
       </c>
       <c r="R5" t="n">
-        <v>7047712</v>
+        <v>7047747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1148,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122568871</v>
+        <v>122566696</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1184,7 +1199,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1193,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577847</v>
+        <v>577752</v>
       </c>
       <c r="R6" t="n">
-        <v>7047657</v>
+        <v>7047671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,12 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,22 +1273,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566643</v>
+        <v>122568906</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,34 +1301,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577816</v>
+        <v>577851</v>
       </c>
       <c r="R7" t="n">
-        <v>7047681</v>
+        <v>7047625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1375,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,19 +1395,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122568670</v>
+        <v>122568144</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1427,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577765</v>
+        <v>577721</v>
       </c>
       <c r="R8" t="n">
-        <v>7047696</v>
+        <v>7047806</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1492,19 +1517,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122568196</v>
+        <v>122568120</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1549,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577717</v>
+        <v>577697</v>
       </c>
       <c r="R9" t="n">
-        <v>7047745</v>
+        <v>7047768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1619,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,7 +1651,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567764</v>
+        <v>122566515</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1662,7 +1687,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1671,13 +1696,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577641</v>
+        <v>577857</v>
       </c>
       <c r="R10" t="n">
-        <v>7047789</v>
+        <v>7047693</v>
       </c>
       <c r="S10" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1741,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,22 +1761,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122568906</v>
+        <v>122567965</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,39 +1789,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577851</v>
+        <v>577621</v>
       </c>
       <c r="R11" t="n">
-        <v>7047625</v>
+        <v>7047786</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1848,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,12 +1858,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,19 +1873,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567250</v>
+        <v>122567603</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1901,7 +1921,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1910,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577683</v>
+        <v>577640</v>
       </c>
       <c r="R12" t="n">
-        <v>7047626</v>
+        <v>7047712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1975,12 +1995,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2109,7 +2129,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566730</v>
+        <v>122568670</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2154,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577749</v>
+        <v>577765</v>
       </c>
       <c r="R14" t="n">
-        <v>7047671</v>
+        <v>7047696</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,7 +2209,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2199,7 +2219,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2219,19 +2239,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567415</v>
+        <v>122568098</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2267,7 +2287,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2276,10 +2296,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577665</v>
+        <v>577684</v>
       </c>
       <c r="R15" t="n">
-        <v>7047625</v>
+        <v>7047782</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,7 +2331,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,12 +2341,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,10 +2373,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566471</v>
+        <v>122566508</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,39 +2389,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577878</v>
+        <v>577875</v>
       </c>
       <c r="R16" t="n">
-        <v>7047667</v>
+        <v>7047661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2448,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2458,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2463,22 +2473,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122568013</v>
+        <v>122566271</v>
       </c>
       <c r="B17" t="n">
-        <v>90944</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2491,37 +2501,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577636</v>
+        <v>577901</v>
       </c>
       <c r="R17" t="n">
-        <v>7047783</v>
+        <v>7047671</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2550,7 +2565,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2560,7 +2575,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2587,10 +2602,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122568052</v>
+        <v>122566768</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2603,34 +2618,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577647</v>
+        <v>577712</v>
       </c>
       <c r="R18" t="n">
-        <v>7047774</v>
+        <v>7047643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2682,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,7 +2692,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2699,10 +2724,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122565992</v>
+        <v>122568052</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,21 +2740,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,10 +2764,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577930</v>
+        <v>577647</v>
       </c>
       <c r="R19" t="n">
-        <v>7047678</v>
+        <v>7047774</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2774,7 +2799,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2784,7 +2809,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2811,7 +2836,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122568922</v>
+        <v>122567764</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2847,7 +2872,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2856,13 +2881,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577858</v>
+        <v>577641</v>
       </c>
       <c r="R20" t="n">
-        <v>7047635</v>
+        <v>7047789</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2891,7 +2916,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2901,12 +2926,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2921,22 +2941,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567115</v>
+        <v>122568123</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,34 +2969,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577719</v>
+        <v>577688</v>
       </c>
       <c r="R21" t="n">
-        <v>7047669</v>
+        <v>7047768</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3008,7 +3033,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3018,7 +3043,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3045,7 +3075,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567761</v>
+        <v>122567250</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -3081,7 +3111,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3090,10 +3120,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577630</v>
+        <v>577683</v>
       </c>
       <c r="R22" t="n">
-        <v>7047750</v>
+        <v>7047626</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3125,7 +3155,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3135,12 +3165,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3155,22 +3185,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567519</v>
+        <v>122566643</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3183,39 +3213,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577659</v>
+        <v>577816</v>
       </c>
       <c r="R23" t="n">
-        <v>7047666</v>
+        <v>7047681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3247,7 +3272,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3257,12 +3282,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3277,22 +3297,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566768</v>
+        <v>122568145</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3305,39 +3325,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577712</v>
+        <v>577696</v>
       </c>
       <c r="R24" t="n">
-        <v>7047643</v>
+        <v>7047755</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3369,7 +3384,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3379,12 +3394,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3411,10 +3421,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122568098</v>
+        <v>122567115</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3427,39 +3437,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577684</v>
+        <v>577719</v>
       </c>
       <c r="R25" t="n">
-        <v>7047782</v>
+        <v>7047669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3496,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,12 +3506,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567856</v>
+        <v>122568013</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3549,39 +3549,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577598</v>
+        <v>577636</v>
       </c>
       <c r="R26" t="n">
-        <v>7047750</v>
+        <v>7047783</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3613,7 +3608,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3623,12 +3618,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3643,19 +3633,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566495</v>
+        <v>122566694</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3700,13 +3690,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577898</v>
+        <v>577770</v>
       </c>
       <c r="R27" t="n">
-        <v>7047638</v>
+        <v>7047663</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3735,7 +3725,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3745,7 +3735,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3765,19 +3755,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122568120</v>
+        <v>122566485</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3822,10 +3812,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577697</v>
+        <v>577908</v>
       </c>
       <c r="R28" t="n">
-        <v>7047768</v>
+        <v>7047646</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3857,7 +3847,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3867,12 +3857,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på två tallar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3887,19 +3877,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122568941</v>
+        <v>122567519</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3944,10 +3934,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577874</v>
+        <v>577659</v>
       </c>
       <c r="R29" t="n">
-        <v>7047636</v>
+        <v>7047666</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,7 +3969,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3989,12 +3979,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4021,10 +4011,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122568836</v>
+        <v>122567600</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4037,34 +4027,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577845</v>
+        <v>577658</v>
       </c>
       <c r="R30" t="n">
-        <v>7047652</v>
+        <v>7047696</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4096,7 +4091,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4106,7 +4101,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4121,22 +4121,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567600</v>
+        <v>122567426</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4149,27 +4149,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4178,10 +4182,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577658</v>
+        <v>577666</v>
       </c>
       <c r="R31" t="n">
-        <v>7047696</v>
+        <v>7047652</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4213,7 +4217,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4223,12 +4227,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4255,7 +4254,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566485</v>
+        <v>122566471</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4300,10 +4299,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577908</v>
+        <v>577878</v>
       </c>
       <c r="R32" t="n">
-        <v>7047646</v>
+        <v>7047667</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4365,22 +4364,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567504</v>
+        <v>122567286</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,39 +4392,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577648</v>
+        <v>577696</v>
       </c>
       <c r="R33" t="n">
-        <v>7047682</v>
+        <v>7047629</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4457,7 +4451,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4467,12 +4461,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4499,10 +4488,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566508</v>
+        <v>122568922</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4515,34 +4504,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577875</v>
+        <v>577858</v>
       </c>
       <c r="R34" t="n">
-        <v>7047661</v>
+        <v>7047635</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4574,7 +4568,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4584,7 +4578,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4599,22 +4598,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122568145</v>
+        <v>122566495</v>
       </c>
       <c r="B35" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4627,37 +4626,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577696</v>
+        <v>577898</v>
       </c>
       <c r="R35" t="n">
-        <v>7047755</v>
+        <v>7047638</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4686,7 +4690,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4696,7 +4700,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4711,19 +4720,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566515</v>
+        <v>122566730</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4768,10 +4777,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577857</v>
+        <v>577749</v>
       </c>
       <c r="R36" t="n">
-        <v>7047693</v>
+        <v>7047671</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4803,7 +4812,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4813,12 +4822,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4833,19 +4842,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567426</v>
+        <v>122565992</v>
       </c>
       <c r="B37" t="n">
         <v>90962</v>
@@ -4878,26 +4887,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577666</v>
+        <v>577930</v>
       </c>
       <c r="R37" t="n">
-        <v>7047652</v>
+        <v>7047678</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4966,10 +4966,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122568144</v>
+        <v>122568836</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4982,39 +4982,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577721</v>
+        <v>577845</v>
       </c>
       <c r="R38" t="n">
-        <v>7047806</v>
+        <v>7047652</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5046,7 +5041,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5056,12 +5051,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5076,19 +5066,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122568123</v>
+        <v>122567761</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5133,10 +5123,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577688</v>
+        <v>577630</v>
       </c>
       <c r="R39" t="n">
-        <v>7047768</v>
+        <v>7047750</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5168,7 +5158,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5178,12 +5168,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5198,19 +5188,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566696</v>
+        <v>122568871</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -5246,7 +5236,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5255,10 +5245,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577752</v>
+        <v>577847</v>
       </c>
       <c r="R40" t="n">
-        <v>7047671</v>
+        <v>7047657</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5290,7 +5280,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5300,12 +5290,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5320,19 +5310,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566494</v>
+        <v>122567415</v>
       </c>
       <c r="B41" t="n">
         <v>57478</v>
@@ -5368,7 +5358,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5377,10 +5367,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577868</v>
+        <v>577665</v>
       </c>
       <c r="R41" t="n">
-        <v>7047668</v>
+        <v>7047625</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5412,7 +5402,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5422,7 +5412,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5442,22 +5432,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567286</v>
+        <v>122566494</v>
       </c>
       <c r="B42" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5470,34 +5460,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577696</v>
+        <v>577868</v>
       </c>
       <c r="R42" t="n">
-        <v>7047629</v>
+        <v>7047668</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5529,7 +5524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5539,7 +5534,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5554,19 +5554,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122568234</v>
+        <v>122567504</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577772</v>
+        <v>577648</v>
       </c>
       <c r="R43" t="n">
-        <v>7047747</v>
+        <v>7047682</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567856</v>
+        <v>122568120</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577598</v>
+        <v>577697</v>
       </c>
       <c r="R2" t="n">
-        <v>7047750</v>
+        <v>7047768</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,19 +785,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122568941</v>
+        <v>122568871</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577874</v>
+        <v>577847</v>
       </c>
       <c r="R3" t="n">
-        <v>7047636</v>
+        <v>7047657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122568196</v>
+        <v>122566495</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577717</v>
+        <v>577898</v>
       </c>
       <c r="R4" t="n">
-        <v>7047745</v>
+        <v>7047638</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,12 +1029,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566696</v>
+        <v>122567603</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1199,7 +1199,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577752</v>
+        <v>577640</v>
       </c>
       <c r="R6" t="n">
-        <v>7047671</v>
+        <v>7047712</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,7 +1285,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122568906</v>
+        <v>122566471</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577851</v>
+        <v>577878</v>
       </c>
       <c r="R7" t="n">
-        <v>7047625</v>
+        <v>7047667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1407,7 +1407,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122568144</v>
+        <v>122566696</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1443,7 +1443,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577721</v>
+        <v>577752</v>
       </c>
       <c r="R8" t="n">
-        <v>7047806</v>
+        <v>7047671</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1529,7 +1529,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122568120</v>
+        <v>122566485</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577697</v>
+        <v>577908</v>
       </c>
       <c r="R9" t="n">
-        <v>7047768</v>
+        <v>7047646</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på två tallar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,22 +1639,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566515</v>
+        <v>122568145</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,39 +1667,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577857</v>
+        <v>577696</v>
       </c>
       <c r="R10" t="n">
-        <v>7047693</v>
+        <v>7047755</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,7 +1726,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1741,12 +1736,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,22 +1751,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567965</v>
+        <v>122567415</v>
       </c>
       <c r="B11" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,34 +1779,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577621</v>
+        <v>577665</v>
       </c>
       <c r="R11" t="n">
-        <v>7047786</v>
+        <v>7047625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1858,7 +1853,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,7 +1885,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567603</v>
+        <v>122566730</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577640</v>
+        <v>577749</v>
       </c>
       <c r="R12" t="n">
-        <v>7047712</v>
+        <v>7047671</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2007,10 +2007,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567649</v>
+        <v>122567115</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2023,39 +2023,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577631</v>
+        <v>577719</v>
       </c>
       <c r="R13" t="n">
-        <v>7047709</v>
+        <v>7047669</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,7 +2082,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,12 +2092,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2129,7 +2119,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122568670</v>
+        <v>122567764</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2165,7 +2155,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2174,13 +2164,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577765</v>
+        <v>577641</v>
       </c>
       <c r="R14" t="n">
-        <v>7047696</v>
+        <v>7047789</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2209,7 +2199,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2219,12 +2209,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,10 +2236,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122568098</v>
+        <v>122568052</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2267,39 +2252,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577684</v>
+        <v>577647</v>
       </c>
       <c r="R15" t="n">
-        <v>7047782</v>
+        <v>7047774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2331,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2341,12 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2361,22 +2336,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566508</v>
+        <v>122568098</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2389,34 +2364,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577875</v>
+        <v>577684</v>
       </c>
       <c r="R16" t="n">
-        <v>7047661</v>
+        <v>7047782</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,7 +2428,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2458,7 +2438,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566271</v>
+        <v>122566694</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2501,27 +2486,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2530,13 +2515,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577901</v>
+        <v>577770</v>
       </c>
       <c r="R17" t="n">
-        <v>7047671</v>
+        <v>7047663</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2565,7 +2550,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2575,7 +2560,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2602,7 +2592,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566768</v>
+        <v>122567519</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2638,7 +2628,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2647,10 +2637,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577712</v>
+        <v>577659</v>
       </c>
       <c r="R18" t="n">
-        <v>7047643</v>
+        <v>7047666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2682,7 +2672,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2692,12 +2682,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2724,10 +2714,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122568052</v>
+        <v>122568123</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2740,34 +2730,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577647</v>
+        <v>577688</v>
       </c>
       <c r="R19" t="n">
-        <v>7047774</v>
+        <v>7047768</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,7 +2794,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2809,7 +2804,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,22 +2824,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567764</v>
+        <v>122566643</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2852,42 +2852,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577641</v>
+        <v>577816</v>
       </c>
       <c r="R20" t="n">
-        <v>7047789</v>
+        <v>7047681</v>
       </c>
       <c r="S20" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2916,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2926,7 +2921,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2941,19 +2936,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568123</v>
+        <v>122568144</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2998,10 +2993,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577688</v>
+        <v>577721</v>
       </c>
       <c r="R21" t="n">
-        <v>7047768</v>
+        <v>7047806</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3033,7 +3028,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3043,7 +3038,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3075,10 +3070,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567250</v>
+        <v>122566508</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,39 +3086,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577683</v>
+        <v>577875</v>
       </c>
       <c r="R22" t="n">
-        <v>7047626</v>
+        <v>7047661</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3155,7 +3145,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3165,12 +3155,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3185,22 +3170,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566643</v>
+        <v>122568013</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3213,21 +3198,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3237,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577816</v>
+        <v>577636</v>
       </c>
       <c r="R23" t="n">
-        <v>7047681</v>
+        <v>7047783</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3272,7 +3257,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3282,7 +3267,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3297,22 +3282,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122568145</v>
+        <v>122567250</v>
       </c>
       <c r="B24" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3325,34 +3310,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577696</v>
+        <v>577683</v>
       </c>
       <c r="R24" t="n">
-        <v>7047755</v>
+        <v>7047626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3384,7 +3374,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3394,7 +3384,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3421,10 +3416,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567115</v>
+        <v>122566271</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3437,37 +3432,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577719</v>
+        <v>577901</v>
       </c>
       <c r="R25" t="n">
-        <v>7047669</v>
+        <v>7047671</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3521,22 +3521,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122568013</v>
+        <v>122566768</v>
       </c>
       <c r="B26" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3549,34 +3549,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577636</v>
+        <v>577712</v>
       </c>
       <c r="R26" t="n">
-        <v>7047783</v>
+        <v>7047643</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3608,7 +3613,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3618,7 +3623,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3645,7 +3655,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566694</v>
+        <v>122568670</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3690,10 +3700,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577770</v>
+        <v>577765</v>
       </c>
       <c r="R27" t="n">
-        <v>7047663</v>
+        <v>7047696</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3725,7 +3735,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3735,7 +3745,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3767,7 +3777,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566485</v>
+        <v>122567649</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3812,10 +3822,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577908</v>
+        <v>577631</v>
       </c>
       <c r="R28" t="n">
-        <v>7047646</v>
+        <v>7047709</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3847,7 +3857,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3857,12 +3867,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3889,7 +3899,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567519</v>
+        <v>122567600</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3934,10 +3944,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577659</v>
+        <v>577658</v>
       </c>
       <c r="R29" t="n">
-        <v>7047666</v>
+        <v>7047696</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3969,7 +3979,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3979,7 +3989,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4011,7 +4021,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567600</v>
+        <v>122566494</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -4056,10 +4066,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577658</v>
+        <v>577868</v>
       </c>
       <c r="R30" t="n">
-        <v>7047696</v>
+        <v>7047668</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4091,7 +4101,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4101,12 +4111,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4133,10 +4143,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567426</v>
+        <v>122567286</v>
       </c>
       <c r="B31" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4149,43 +4159,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577666</v>
+        <v>577696</v>
       </c>
       <c r="R31" t="n">
-        <v>7047652</v>
+        <v>7047629</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4217,7 +4218,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4227,7 +4228,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4242,22 +4243,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566471</v>
+        <v>122567965</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4270,39 +4271,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577878</v>
+        <v>577621</v>
       </c>
       <c r="R32" t="n">
-        <v>7047667</v>
+        <v>7047786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4334,7 +4330,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4344,12 +4340,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4364,22 +4355,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567286</v>
+        <v>122567761</v>
       </c>
       <c r="B33" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4392,34 +4383,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577696</v>
+        <v>577630</v>
       </c>
       <c r="R33" t="n">
-        <v>7047629</v>
+        <v>7047750</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4451,7 +4447,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4461,7 +4457,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4476,19 +4477,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122568922</v>
+        <v>122566515</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4533,10 +4534,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577858</v>
+        <v>577857</v>
       </c>
       <c r="R34" t="n">
-        <v>7047635</v>
+        <v>7047693</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4568,7 +4569,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4578,7 +4579,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4598,22 +4599,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566495</v>
+        <v>122565992</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4626,42 +4627,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577898</v>
+        <v>577930</v>
       </c>
       <c r="R35" t="n">
-        <v>7047638</v>
+        <v>7047678</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4690,7 +4686,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4700,12 +4696,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4720,19 +4711,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566730</v>
+        <v>122567856</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4777,10 +4768,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577749</v>
+        <v>577598</v>
       </c>
       <c r="R36" t="n">
-        <v>7047671</v>
+        <v>7047750</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4812,7 +4803,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4822,7 +4813,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4854,10 +4845,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122565992</v>
+        <v>122568922</v>
       </c>
       <c r="B37" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4870,34 +4861,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577930</v>
+        <v>577858</v>
       </c>
       <c r="R37" t="n">
-        <v>7047678</v>
+        <v>7047635</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4929,7 +4925,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4939,7 +4935,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4954,12 +4955,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5078,7 +5079,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567761</v>
+        <v>122568906</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5123,10 +5124,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577630</v>
+        <v>577851</v>
       </c>
       <c r="R39" t="n">
-        <v>7047750</v>
+        <v>7047625</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5158,7 +5159,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5168,7 +5169,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5188,19 +5189,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122568871</v>
+        <v>122568196</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -5245,10 +5246,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577847</v>
+        <v>577717</v>
       </c>
       <c r="R40" t="n">
-        <v>7047657</v>
+        <v>7047745</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5280,7 +5281,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5290,12 +5291,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5322,10 +5323,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567415</v>
+        <v>122567426</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5338,27 +5339,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5367,10 +5372,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577665</v>
+        <v>577666</v>
       </c>
       <c r="R41" t="n">
-        <v>7047625</v>
+        <v>7047652</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5402,7 +5407,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5412,12 +5417,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5432,19 +5432,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566494</v>
+        <v>122568941</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577868</v>
+        <v>577874</v>
       </c>
       <c r="R42" t="n">
-        <v>7047668</v>
+        <v>7047636</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567603</v>
+        <v>122566696</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1199,7 +1199,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577640</v>
+        <v>577752</v>
       </c>
       <c r="R6" t="n">
-        <v>7047712</v>
+        <v>7047671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,7 +1285,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566471</v>
+        <v>122566485</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577878</v>
+        <v>577908</v>
       </c>
       <c r="R7" t="n">
-        <v>7047667</v>
+        <v>7047646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1395,19 +1395,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566696</v>
+        <v>122567603</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1443,7 +1443,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577752</v>
+        <v>577640</v>
       </c>
       <c r="R8" t="n">
-        <v>7047671</v>
+        <v>7047712</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1529,7 +1529,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566485</v>
+        <v>122566471</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577908</v>
+        <v>577878</v>
       </c>
       <c r="R9" t="n">
-        <v>7047646</v>
+        <v>7047667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,22 +1639,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122568145</v>
+        <v>122567415</v>
       </c>
       <c r="B10" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,34 +1667,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577696</v>
+        <v>577665</v>
       </c>
       <c r="R10" t="n">
-        <v>7047755</v>
+        <v>7047625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1726,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1736,7 +1741,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1751,22 +1761,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567415</v>
+        <v>122568145</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1779,39 +1789,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577665</v>
+        <v>577696</v>
       </c>
       <c r="R11" t="n">
-        <v>7047625</v>
+        <v>7047755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1848,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,12 +1858,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,22 +1873,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566730</v>
+        <v>122567115</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1901,39 +1901,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577749</v>
+        <v>577719</v>
       </c>
       <c r="R12" t="n">
-        <v>7047671</v>
+        <v>7047669</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1960,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,12 +1970,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2007,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567115</v>
+        <v>122566730</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2023,34 +2013,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577719</v>
+        <v>577749</v>
       </c>
       <c r="R13" t="n">
-        <v>7047669</v>
+        <v>7047671</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,7 +2077,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,7 +2087,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567519</v>
+        <v>122566643</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,39 +2608,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577659</v>
+        <v>577816</v>
       </c>
       <c r="R18" t="n">
-        <v>7047666</v>
+        <v>7047681</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2672,7 +2667,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2682,12 +2677,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2702,19 +2692,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122568123</v>
+        <v>122567519</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2759,10 +2749,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577688</v>
+        <v>577659</v>
       </c>
       <c r="R19" t="n">
-        <v>7047768</v>
+        <v>7047666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2794,7 +2784,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2804,7 +2794,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2824,22 +2814,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566643</v>
+        <v>122568123</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2852,34 +2842,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577816</v>
+        <v>577688</v>
       </c>
       <c r="R20" t="n">
-        <v>7047681</v>
+        <v>7047768</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2911,7 +2906,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,7 +2916,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,10 +2948,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568144</v>
+        <v>122566508</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2964,39 +2964,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577721</v>
+        <v>577875</v>
       </c>
       <c r="R21" t="n">
-        <v>7047806</v>
+        <v>7047661</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3028,7 +3023,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3038,12 +3033,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3070,10 +3060,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566508</v>
+        <v>122568144</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3086,34 +3076,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577875</v>
+        <v>577721</v>
       </c>
       <c r="R22" t="n">
-        <v>7047661</v>
+        <v>7047806</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,7 +3140,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3155,7 +3150,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4021,10 +4021,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566494</v>
+        <v>122567286</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4037,39 +4037,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577868</v>
+        <v>577696</v>
       </c>
       <c r="R30" t="n">
-        <v>7047668</v>
+        <v>7047629</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4101,7 +4096,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4111,12 +4106,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4131,19 +4121,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567286</v>
+        <v>122567965</v>
       </c>
       <c r="B31" t="n">
         <v>90944</v>
@@ -4183,10 +4173,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577696</v>
+        <v>577621</v>
       </c>
       <c r="R31" t="n">
-        <v>7047629</v>
+        <v>7047786</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4218,7 +4208,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4228,7 +4218,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4255,10 +4245,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567965</v>
+        <v>122566494</v>
       </c>
       <c r="B32" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4271,34 +4261,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577621</v>
+        <v>577868</v>
       </c>
       <c r="R32" t="n">
-        <v>7047786</v>
+        <v>7047668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4330,7 +4325,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4340,7 +4335,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4355,12 +4355,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566696</v>
+        <v>122567603</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1199,7 +1199,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577752</v>
+        <v>577640</v>
       </c>
       <c r="R6" t="n">
-        <v>7047671</v>
+        <v>7047712</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,7 +1285,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566485</v>
+        <v>122566471</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577908</v>
+        <v>577878</v>
       </c>
       <c r="R7" t="n">
-        <v>7047646</v>
+        <v>7047667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1395,19 +1395,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567603</v>
+        <v>122566696</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1443,7 +1443,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577640</v>
+        <v>577752</v>
       </c>
       <c r="R8" t="n">
-        <v>7047712</v>
+        <v>7047671</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1529,7 +1529,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566471</v>
+        <v>122566485</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577878</v>
+        <v>577908</v>
       </c>
       <c r="R9" t="n">
-        <v>7047667</v>
+        <v>7047646</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,12 +1639,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567115</v>
+        <v>122566730</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1901,34 +1901,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577719</v>
+        <v>577749</v>
       </c>
       <c r="R12" t="n">
-        <v>7047669</v>
+        <v>7047671</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1960,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1970,7 +1975,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,10 +2007,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566730</v>
+        <v>122567115</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,39 +2023,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577749</v>
+        <v>577719</v>
       </c>
       <c r="R13" t="n">
-        <v>7047671</v>
+        <v>7047669</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2077,7 +2082,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2087,12 +2092,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566643</v>
+        <v>122567519</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,34 +2608,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577816</v>
+        <v>577659</v>
       </c>
       <c r="R18" t="n">
-        <v>7047681</v>
+        <v>7047666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2667,7 +2672,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2677,7 +2682,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,19 +2702,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567519</v>
+        <v>122568123</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2749,10 +2759,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577659</v>
+        <v>577688</v>
       </c>
       <c r="R19" t="n">
-        <v>7047666</v>
+        <v>7047768</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2784,7 +2794,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2794,7 +2804,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2814,22 +2824,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122568123</v>
+        <v>122566643</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2842,39 +2852,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577688</v>
+        <v>577816</v>
       </c>
       <c r="R20" t="n">
-        <v>7047768</v>
+        <v>7047681</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2916,12 +2921,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122568120</v>
+        <v>122567761</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577697</v>
+        <v>577630</v>
       </c>
       <c r="R2" t="n">
-        <v>7047768</v>
+        <v>7047750</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på två tallar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122568871</v>
+        <v>122567286</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577847</v>
+        <v>577696</v>
       </c>
       <c r="R3" t="n">
-        <v>7047657</v>
+        <v>7047629</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566495</v>
+        <v>122568144</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -964,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577898</v>
+        <v>577721</v>
       </c>
       <c r="R4" t="n">
-        <v>7047638</v>
+        <v>7047806</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122568234</v>
+        <v>122568120</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1086,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577772</v>
+        <v>577697</v>
       </c>
       <c r="R5" t="n">
-        <v>7047747</v>
+        <v>7047768</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567603</v>
+        <v>122566643</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,39 +1169,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577640</v>
+        <v>577816</v>
       </c>
       <c r="R6" t="n">
-        <v>7047712</v>
+        <v>7047681</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566471</v>
+        <v>122568871</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1330,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577878</v>
+        <v>577847</v>
       </c>
       <c r="R7" t="n">
-        <v>7047667</v>
+        <v>7047657</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1407,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566696</v>
+        <v>122568145</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1423,39 +1403,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577752</v>
+        <v>577696</v>
       </c>
       <c r="R8" t="n">
-        <v>7047671</v>
+        <v>7047755</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,19 +1487,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566485</v>
+        <v>122566694</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1574,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577908</v>
+        <v>577770</v>
       </c>
       <c r="R9" t="n">
-        <v>7047646</v>
+        <v>7047663</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1619,12 +1589,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,19 +1609,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567415</v>
+        <v>122566515</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1687,7 +1657,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1696,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577665</v>
+        <v>577857</v>
       </c>
       <c r="R10" t="n">
-        <v>7047625</v>
+        <v>7047693</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1741,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1761,22 +1731,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122568145</v>
+        <v>122567250</v>
       </c>
       <c r="B11" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,34 +1759,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577696</v>
+        <v>577683</v>
       </c>
       <c r="R11" t="n">
-        <v>7047755</v>
+        <v>7047626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1858,7 +1833,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566730</v>
+        <v>122568013</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1901,39 +1881,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577749</v>
+        <v>577636</v>
       </c>
       <c r="R12" t="n">
-        <v>7047671</v>
+        <v>7047783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,12 +1950,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,22 +1965,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567115</v>
+        <v>122567649</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2023,34 +1993,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577719</v>
+        <v>577631</v>
       </c>
       <c r="R13" t="n">
-        <v>7047669</v>
+        <v>7047709</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,7 +2057,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,7 +2067,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,7 +2099,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567764</v>
+        <v>122568906</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2155,7 +2135,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2164,13 +2144,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577641</v>
+        <v>577851</v>
       </c>
       <c r="R14" t="n">
-        <v>7047789</v>
+        <v>7047625</v>
       </c>
       <c r="S14" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2199,7 +2179,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2209,7 +2189,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2236,10 +2221,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122568052</v>
+        <v>122568123</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,34 +2237,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577647</v>
+        <v>577688</v>
       </c>
       <c r="R15" t="n">
-        <v>7047774</v>
+        <v>7047768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,7 +2301,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2311,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,19 +2331,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122568098</v>
+        <v>122567519</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2393,10 +2388,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577684</v>
+        <v>577659</v>
       </c>
       <c r="R16" t="n">
-        <v>7047782</v>
+        <v>7047666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2428,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2438,7 +2433,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2458,19 +2453,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566694</v>
+        <v>122568098</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2515,10 +2510,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577770</v>
+        <v>577684</v>
       </c>
       <c r="R17" t="n">
-        <v>7047663</v>
+        <v>7047782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2550,7 +2545,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2560,7 +2555,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2580,19 +2575,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567519</v>
+        <v>122566730</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2637,10 +2632,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577659</v>
+        <v>577749</v>
       </c>
       <c r="R18" t="n">
-        <v>7047666</v>
+        <v>7047671</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2672,7 +2667,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2682,7 +2677,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2702,19 +2697,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122568123</v>
+        <v>122568922</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2759,10 +2754,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577688</v>
+        <v>577858</v>
       </c>
       <c r="R19" t="n">
-        <v>7047768</v>
+        <v>7047635</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2794,7 +2789,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2804,12 +2799,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,22 +2819,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566643</v>
+        <v>122568196</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2852,34 +2847,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577816</v>
+        <v>577717</v>
       </c>
       <c r="R20" t="n">
-        <v>7047681</v>
+        <v>7047745</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,7 +2921,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2936,22 +2941,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566508</v>
+        <v>122568052</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2964,21 +2969,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2988,10 +2993,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577875</v>
+        <v>577647</v>
       </c>
       <c r="R21" t="n">
-        <v>7047661</v>
+        <v>7047774</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3023,7 +3028,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3033,7 +3038,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,19 +3053,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122568144</v>
+        <v>122566485</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -3105,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577721</v>
+        <v>577908</v>
       </c>
       <c r="R22" t="n">
-        <v>7047806</v>
+        <v>7047646</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3140,7 +3145,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3150,12 +3155,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3182,7 +3187,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122568013</v>
+        <v>122567965</v>
       </c>
       <c r="B23" t="n">
         <v>90944</v>
@@ -3222,10 +3227,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577636</v>
+        <v>577621</v>
       </c>
       <c r="R23" t="n">
-        <v>7047783</v>
+        <v>7047786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3257,7 +3262,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3267,7 +3272,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3282,22 +3287,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567250</v>
+        <v>122566508</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3310,39 +3315,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577683</v>
+        <v>577875</v>
       </c>
       <c r="R24" t="n">
-        <v>7047626</v>
+        <v>7047661</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3384,12 +3384,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3404,22 +3399,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566271</v>
+        <v>122566768</v>
       </c>
       <c r="B25" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3432,27 +3427,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3461,13 +3456,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577901</v>
+        <v>577712</v>
       </c>
       <c r="R25" t="n">
-        <v>7047671</v>
+        <v>7047643</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3496,7 +3491,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3506,7 +3501,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3533,7 +3533,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566768</v>
+        <v>122567764</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3569,7 +3569,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577712</v>
+        <v>577641</v>
       </c>
       <c r="R26" t="n">
-        <v>7047643</v>
+        <v>7047789</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3623,12 +3623,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3655,7 +3650,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122568670</v>
+        <v>122566494</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3700,10 +3695,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577765</v>
+        <v>577868</v>
       </c>
       <c r="R27" t="n">
-        <v>7047696</v>
+        <v>7047668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3735,7 +3730,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3745,12 +3740,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3777,7 +3772,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567649</v>
+        <v>122568941</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3822,10 +3817,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577631</v>
+        <v>577874</v>
       </c>
       <c r="R28" t="n">
-        <v>7047709</v>
+        <v>7047636</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3857,7 +3852,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3867,12 +3862,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3887,19 +3882,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567600</v>
+        <v>122568234</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3944,10 +3939,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577658</v>
+        <v>577772</v>
       </c>
       <c r="R29" t="n">
-        <v>7047696</v>
+        <v>7047747</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3989,7 +3984,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4009,22 +4004,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567286</v>
+        <v>122567504</v>
       </c>
       <c r="B30" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4037,34 +4032,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577696</v>
+        <v>577648</v>
       </c>
       <c r="R30" t="n">
-        <v>7047629</v>
+        <v>7047682</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4106,7 +4106,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4133,10 +4138,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567965</v>
+        <v>122567856</v>
       </c>
       <c r="B31" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4149,34 +4154,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577621</v>
+        <v>577598</v>
       </c>
       <c r="R31" t="n">
-        <v>7047786</v>
+        <v>7047750</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4208,7 +4218,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4218,7 +4228,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4245,7 +4260,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566494</v>
+        <v>122567600</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4290,10 +4305,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577868</v>
+        <v>577658</v>
       </c>
       <c r="R32" t="n">
-        <v>7047668</v>
+        <v>7047696</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4325,7 +4340,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4335,12 +4350,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4367,10 +4382,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567761</v>
+        <v>122567426</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4383,27 +4398,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4412,10 +4431,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577630</v>
+        <v>577666</v>
       </c>
       <c r="R33" t="n">
-        <v>7047750</v>
+        <v>7047652</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4447,7 +4466,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4457,12 +4476,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4477,22 +4491,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566515</v>
+        <v>122568836</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4505,39 +4519,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577857</v>
+        <v>577845</v>
       </c>
       <c r="R34" t="n">
-        <v>7047693</v>
+        <v>7047652</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4569,7 +4578,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4579,12 +4588,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4599,22 +4603,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122565992</v>
+        <v>122567603</v>
       </c>
       <c r="B35" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4627,34 +4631,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577930</v>
+        <v>577640</v>
       </c>
       <c r="R35" t="n">
-        <v>7047678</v>
+        <v>7047712</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4686,7 +4695,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4696,7 +4705,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4711,22 +4725,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567856</v>
+        <v>122565992</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4739,39 +4753,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577598</v>
+        <v>577930</v>
       </c>
       <c r="R36" t="n">
-        <v>7047750</v>
+        <v>7047678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4803,7 +4812,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4813,12 +4822,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4833,22 +4837,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122568922</v>
+        <v>122566271</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4861,27 +4865,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4890,13 +4894,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577858</v>
+        <v>577901</v>
       </c>
       <c r="R37" t="n">
-        <v>7047635</v>
+        <v>7047671</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4925,7 +4929,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4935,12 +4939,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4955,22 +4954,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122568836</v>
+        <v>122567115</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4983,21 +4982,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5007,10 +5006,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577845</v>
+        <v>577719</v>
       </c>
       <c r="R38" t="n">
-        <v>7047652</v>
+        <v>7047669</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5042,7 +5041,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5052,7 +5051,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5067,19 +5066,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122568906</v>
+        <v>122568670</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5124,10 +5123,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577851</v>
+        <v>577765</v>
       </c>
       <c r="R39" t="n">
-        <v>7047625</v>
+        <v>7047696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5159,7 +5158,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5169,12 +5168,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5201,7 +5200,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122568196</v>
+        <v>122566495</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -5246,13 +5245,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577717</v>
+        <v>577898</v>
       </c>
       <c r="R40" t="n">
-        <v>7047745</v>
+        <v>7047638</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5281,7 +5280,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5291,7 +5290,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5311,22 +5310,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567426</v>
+        <v>122566696</v>
       </c>
       <c r="B41" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5339,31 +5338,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5372,10 +5367,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577666</v>
+        <v>577752</v>
       </c>
       <c r="R41" t="n">
-        <v>7047652</v>
+        <v>7047671</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5407,7 +5402,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5417,7 +5412,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5432,19 +5432,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122568941</v>
+        <v>122566471</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577874</v>
+        <v>577878</v>
       </c>
       <c r="R42" t="n">
-        <v>7047636</v>
+        <v>7047667</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5566,7 +5566,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567504</v>
+        <v>122567415</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5602,7 +5602,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577648</v>
+        <v>577665</v>
       </c>
       <c r="R43" t="n">
-        <v>7047682</v>
+        <v>7047625</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567286</v>
+        <v>122568871</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577696</v>
+        <v>577847</v>
       </c>
       <c r="R3" t="n">
-        <v>7047629</v>
+        <v>7047657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122568144</v>
+        <v>122567286</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577721</v>
+        <v>577696</v>
       </c>
       <c r="R4" t="n">
-        <v>7047806</v>
+        <v>7047629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122568120</v>
+        <v>122566643</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577697</v>
+        <v>577816</v>
       </c>
       <c r="R5" t="n">
-        <v>7047768</v>
+        <v>7047681</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på två tallar</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566643</v>
+        <v>122568144</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,34 +1159,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577816</v>
+        <v>577721</v>
       </c>
       <c r="R6" t="n">
-        <v>7047681</v>
+        <v>7047806</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122568871</v>
+        <v>122568120</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577847</v>
+        <v>577697</v>
       </c>
       <c r="R7" t="n">
-        <v>7047657</v>
+        <v>7047768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568052</v>
+        <v>122566485</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2969,34 +2969,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577647</v>
+        <v>577908</v>
       </c>
       <c r="R21" t="n">
-        <v>7047774</v>
+        <v>7047646</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3028,7 +3033,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3038,7 +3043,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3053,22 +3063,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566485</v>
+        <v>122568052</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3081,39 +3091,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577908</v>
+        <v>577647</v>
       </c>
       <c r="R22" t="n">
-        <v>7047646</v>
+        <v>7047774</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,7 +3150,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3155,12 +3160,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3175,22 +3175,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567965</v>
+        <v>122566768</v>
       </c>
       <c r="B23" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3203,34 +3203,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577621</v>
+        <v>577712</v>
       </c>
       <c r="R23" t="n">
-        <v>7047786</v>
+        <v>7047643</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3262,7 +3267,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3272,7 +3277,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3287,22 +3297,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566508</v>
+        <v>122567764</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3315,37 +3325,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577875</v>
+        <v>577641</v>
       </c>
       <c r="R24" t="n">
-        <v>7047661</v>
+        <v>7047789</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3374,7 +3389,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3384,7 +3399,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3399,22 +3414,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566768</v>
+        <v>122567965</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3427,39 +3442,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577712</v>
+        <v>577621</v>
       </c>
       <c r="R25" t="n">
-        <v>7047643</v>
+        <v>7047786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3501,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,12 +3511,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3521,22 +3526,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567764</v>
+        <v>122566508</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3549,42 +3554,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577641</v>
+        <v>577875</v>
       </c>
       <c r="R26" t="n">
-        <v>7047789</v>
+        <v>7047661</v>
       </c>
       <c r="S26" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3638,19 +3638,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566494</v>
+        <v>122568941</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577868</v>
+        <v>577874</v>
       </c>
       <c r="R27" t="n">
-        <v>7047668</v>
+        <v>7047636</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3772,7 +3772,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122568941</v>
+        <v>122566494</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577874</v>
+        <v>577868</v>
       </c>
       <c r="R28" t="n">
-        <v>7047636</v>
+        <v>7047668</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122568871</v>
+        <v>122567286</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577847</v>
+        <v>577696</v>
       </c>
       <c r="R3" t="n">
-        <v>7047657</v>
+        <v>7047629</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567286</v>
+        <v>122568144</v>
       </c>
       <c r="B4" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577696</v>
+        <v>577721</v>
       </c>
       <c r="R4" t="n">
-        <v>7047629</v>
+        <v>7047806</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566643</v>
+        <v>122568120</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1047,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577816</v>
+        <v>577697</v>
       </c>
       <c r="R5" t="n">
-        <v>7047681</v>
+        <v>7047768</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122568144</v>
+        <v>122566643</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,39 +1169,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577721</v>
+        <v>577816</v>
       </c>
       <c r="R6" t="n">
-        <v>7047806</v>
+        <v>7047681</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122568120</v>
+        <v>122568871</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577697</v>
+        <v>577847</v>
       </c>
       <c r="R7" t="n">
-        <v>7047768</v>
+        <v>7047657</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på två tallar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566485</v>
+        <v>122568052</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2969,39 +2969,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577908</v>
+        <v>577647</v>
       </c>
       <c r="R21" t="n">
-        <v>7047646</v>
+        <v>7047774</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3033,7 +3028,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3043,12 +3038,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3063,22 +3053,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122568052</v>
+        <v>122566485</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,34 +3081,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577647</v>
+        <v>577908</v>
       </c>
       <c r="R22" t="n">
-        <v>7047774</v>
+        <v>7047646</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3150,7 +3145,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3160,7 +3155,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3175,22 +3175,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566768</v>
+        <v>122567965</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3203,39 +3203,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577712</v>
+        <v>577621</v>
       </c>
       <c r="R23" t="n">
-        <v>7047643</v>
+        <v>7047786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3267,7 +3262,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3277,12 +3272,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3297,22 +3287,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567764</v>
+        <v>122566508</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3325,42 +3315,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577641</v>
+        <v>577875</v>
       </c>
       <c r="R24" t="n">
-        <v>7047789</v>
+        <v>7047661</v>
       </c>
       <c r="S24" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3389,7 +3374,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3399,7 +3384,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3414,22 +3399,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567965</v>
+        <v>122566768</v>
       </c>
       <c r="B25" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3442,34 +3427,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577621</v>
+        <v>577712</v>
       </c>
       <c r="R25" t="n">
-        <v>7047786</v>
+        <v>7047643</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3501,7 +3491,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3511,7 +3501,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3526,22 +3521,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566508</v>
+        <v>122567764</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3554,37 +3549,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577875</v>
+        <v>577641</v>
       </c>
       <c r="R26" t="n">
-        <v>7047661</v>
+        <v>7047789</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3638,19 +3638,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122568941</v>
+        <v>122566494</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577874</v>
+        <v>577868</v>
       </c>
       <c r="R27" t="n">
-        <v>7047636</v>
+        <v>7047668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3772,7 +3772,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566494</v>
+        <v>122568941</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577868</v>
+        <v>577874</v>
       </c>
       <c r="R28" t="n">
-        <v>7047668</v>
+        <v>7047636</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4503,10 +4503,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122568836</v>
+        <v>122566271</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4519,37 +4519,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577845</v>
+        <v>577901</v>
       </c>
       <c r="R34" t="n">
-        <v>7047652</v>
+        <v>7047671</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4578,7 +4583,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4588,7 +4593,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4603,22 +4608,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567603</v>
+        <v>122565992</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4631,39 +4636,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577640</v>
+        <v>577930</v>
       </c>
       <c r="R35" t="n">
-        <v>7047712</v>
+        <v>7047678</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4705,12 +4705,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4725,22 +4720,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122565992</v>
+        <v>122567115</v>
       </c>
       <c r="B36" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4753,21 +4748,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4777,10 +4772,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577930</v>
+        <v>577719</v>
       </c>
       <c r="R36" t="n">
-        <v>7047678</v>
+        <v>7047669</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4812,7 +4807,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4822,7 +4817,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4837,22 +4832,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566271</v>
+        <v>122568836</v>
       </c>
       <c r="B37" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4865,42 +4860,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577901</v>
+        <v>577845</v>
       </c>
       <c r="R37" t="n">
-        <v>7047671</v>
+        <v>7047652</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4929,7 +4919,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4939,7 +4929,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4954,22 +4944,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567115</v>
+        <v>122567603</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4982,34 +4972,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577719</v>
+        <v>577640</v>
       </c>
       <c r="R38" t="n">
-        <v>7047669</v>
+        <v>7047712</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5041,7 +5036,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5051,7 +5046,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567761</v>
+        <v>122567286</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577630</v>
+        <v>577696</v>
       </c>
       <c r="R2" t="n">
-        <v>7047750</v>
+        <v>7047629</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567286</v>
+        <v>122567965</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577696</v>
+        <v>577621</v>
       </c>
       <c r="R3" t="n">
-        <v>7047629</v>
+        <v>7047786</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122568144</v>
+        <v>122568013</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577721</v>
+        <v>577636</v>
       </c>
       <c r="R4" t="n">
-        <v>7047806</v>
+        <v>7047783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,27 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122568120</v>
+        <v>122568145</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577697</v>
+        <v>577696</v>
       </c>
       <c r="R5" t="n">
-        <v>7047768</v>
+        <v>7047755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på två tallar</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,19 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566643</v>
+        <v>122565767</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1193,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577816</v>
+        <v>577991</v>
       </c>
       <c r="R6" t="n">
-        <v>7047681</v>
+        <v>7047591</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,55 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122568871</v>
+        <v>122566508</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577847</v>
+        <v>577875</v>
       </c>
       <c r="R7" t="n">
-        <v>7047657</v>
+        <v>7047661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,49 +1305,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122568145</v>
+        <v>122566643</v>
       </c>
       <c r="B8" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577696</v>
+        <v>577816</v>
       </c>
       <c r="R8" t="n">
-        <v>7047755</v>
+        <v>7047681</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,67 +1412,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566694</v>
+        <v>122567115</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577770</v>
+        <v>577719</v>
       </c>
       <c r="R9" t="n">
-        <v>7047663</v>
+        <v>7047669</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,27 +1519,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566515</v>
+        <v>122568052</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,39 +1542,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577857</v>
+        <v>577647</v>
       </c>
       <c r="R10" t="n">
-        <v>7047693</v>
+        <v>7047774</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,12 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,27 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Romeo Altera</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567250</v>
+        <v>122568836</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,39 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577683</v>
+        <v>577845</v>
       </c>
       <c r="R11" t="n">
-        <v>7047626</v>
+        <v>7047652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,12 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,27 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122568013</v>
+        <v>122566471</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,34 +1756,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577636</v>
+        <v>577878</v>
       </c>
       <c r="R12" t="n">
-        <v>7047783</v>
+        <v>7047667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,7 +1830,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,15 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567649</v>
+        <v>122566485</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577631</v>
+        <v>577908</v>
       </c>
       <c r="R13" t="n">
-        <v>7047709</v>
+        <v>7047646</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2067,12 +1947,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2099,15 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122568906</v>
+        <v>122566494</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577851</v>
+        <v>577868</v>
       </c>
       <c r="R14" t="n">
-        <v>7047625</v>
+        <v>7047668</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2179,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2189,7 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2221,15 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122568123</v>
+        <v>122566495</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,13 +2136,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577688</v>
+        <v>577898</v>
       </c>
       <c r="R15" t="n">
-        <v>7047768</v>
+        <v>7047638</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2301,7 +2171,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2311,7 +2181,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2343,15 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567519</v>
+        <v>122566515</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577659</v>
+        <v>577857</v>
       </c>
       <c r="R16" t="n">
-        <v>7047666</v>
+        <v>7047693</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2423,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2433,12 +2298,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2453,27 +2318,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Romeo Altera</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122568098</v>
+        <v>122566694</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577684</v>
+        <v>577770</v>
       </c>
       <c r="R17" t="n">
-        <v>7047782</v>
+        <v>7047663</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2545,7 +2405,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2555,7 +2415,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2575,27 +2435,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566730</v>
+        <v>122566696</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2478,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2632,7 +2487,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577749</v>
+        <v>577752</v>
       </c>
       <c r="R18" t="n">
         <v>7047671</v>
@@ -2667,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2677,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2709,15 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122568922</v>
+        <v>122566730</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577858</v>
+        <v>577749</v>
       </c>
       <c r="R19" t="n">
-        <v>7047635</v>
+        <v>7047671</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2789,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2799,12 +2649,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,27 +2669,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122568196</v>
+        <v>122566768</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2712,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2876,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577717</v>
+        <v>577712</v>
       </c>
       <c r="R20" t="n">
-        <v>7047745</v>
+        <v>7047643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2911,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,12 +2766,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,15 +2798,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122568052</v>
+        <v>122567250</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2969,34 +2809,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577647</v>
+        <v>577683</v>
       </c>
       <c r="R21" t="n">
-        <v>7047774</v>
+        <v>7047626</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3028,7 +2873,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3038,7 +2883,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3065,15 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566485</v>
+        <v>122567415</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3101,7 +2946,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3110,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577908</v>
+        <v>577665</v>
       </c>
       <c r="R22" t="n">
-        <v>7047646</v>
+        <v>7047625</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3155,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3187,15 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567965</v>
+        <v>122567504</v>
       </c>
       <c r="B23" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,34 +3043,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577621</v>
+        <v>577648</v>
       </c>
       <c r="R23" t="n">
-        <v>7047786</v>
+        <v>7047682</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3262,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3272,7 +3117,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3299,15 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566508</v>
+        <v>122567519</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3315,34 +3160,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577875</v>
+        <v>577659</v>
       </c>
       <c r="R24" t="n">
-        <v>7047661</v>
+        <v>7047666</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3374,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3384,7 +3234,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3399,27 +3254,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566768</v>
+        <v>122567600</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3297,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3456,10 +3306,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577712</v>
+        <v>577658</v>
       </c>
       <c r="R25" t="n">
-        <v>7047643</v>
+        <v>7047696</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,12 +3351,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3533,15 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567764</v>
+        <v>122567603</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3569,7 +3414,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3578,13 +3423,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577641</v>
+        <v>577640</v>
       </c>
       <c r="R26" t="n">
-        <v>7047789</v>
+        <v>7047712</v>
       </c>
       <c r="S26" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3613,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3623,7 +3468,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3638,27 +3488,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566494</v>
+        <v>122567649</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577868</v>
+        <v>577631</v>
       </c>
       <c r="R27" t="n">
-        <v>7047668</v>
+        <v>7047709</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3730,7 +3575,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3740,12 +3585,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,27 +3605,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122568941</v>
+        <v>122567761</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3817,10 +3657,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577874</v>
+        <v>577630</v>
       </c>
       <c r="R28" t="n">
-        <v>7047636</v>
+        <v>7047750</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3852,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3862,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3882,27 +3722,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122568234</v>
+        <v>122567764</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3930,7 +3765,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3939,13 +3774,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577772</v>
+        <v>577641</v>
       </c>
       <c r="R29" t="n">
-        <v>7047747</v>
+        <v>7047789</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3974,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4004,27 +3834,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567504</v>
+        <v>122567856</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4061,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577648</v>
+        <v>577598</v>
       </c>
       <c r="R30" t="n">
-        <v>7047682</v>
+        <v>7047750</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4096,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4106,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4138,15 +3963,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567856</v>
+        <v>122568098</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4183,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577598</v>
+        <v>577684</v>
       </c>
       <c r="R31" t="n">
-        <v>7047750</v>
+        <v>7047782</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4218,7 +4038,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4228,7 +4048,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4260,15 +4080,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567600</v>
+        <v>122568120</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4305,10 +4120,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577658</v>
+        <v>577697</v>
       </c>
       <c r="R32" t="n">
-        <v>7047696</v>
+        <v>7047768</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4340,7 +4155,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4350,12 +4165,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4382,15 +4197,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567426</v>
+        <v>122568123</v>
       </c>
       <c r="B33" t="n">
-        <v>90962</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4398,31 +4208,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4431,10 +4237,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577666</v>
+        <v>577688</v>
       </c>
       <c r="R33" t="n">
-        <v>7047652</v>
+        <v>7047768</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4466,7 +4272,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4476,7 +4282,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4491,27 +4302,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566271</v>
+        <v>122568144</v>
       </c>
       <c r="B34" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4519,27 +4325,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4548,13 +4354,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577901</v>
+        <v>577721</v>
       </c>
       <c r="R34" t="n">
-        <v>7047671</v>
+        <v>7047806</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4583,7 +4389,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4593,7 +4399,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4608,27 +4419,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122565992</v>
+        <v>122568196</v>
       </c>
       <c r="B35" t="n">
-        <v>90962</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4636,34 +4442,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577930</v>
+        <v>577717</v>
       </c>
       <c r="R35" t="n">
-        <v>7047678</v>
+        <v>7047745</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4695,7 +4506,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4705,7 +4516,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4732,15 +4548,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567115</v>
+        <v>122568234</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4748,34 +4559,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577719</v>
+        <v>577772</v>
       </c>
       <c r="R36" t="n">
-        <v>7047669</v>
+        <v>7047747</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4807,7 +4623,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4817,7 +4633,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4844,15 +4665,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122568836</v>
+        <v>122568670</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4860,34 +4676,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577845</v>
+        <v>577765</v>
       </c>
       <c r="R37" t="n">
-        <v>7047652</v>
+        <v>7047696</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4919,7 +4740,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4929,7 +4750,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4944,27 +4770,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567603</v>
+        <v>122568871</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5001,10 +4822,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577640</v>
+        <v>577847</v>
       </c>
       <c r="R38" t="n">
-        <v>7047712</v>
+        <v>7047657</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5036,7 +4857,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5046,12 +4867,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5066,27 +4887,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122568670</v>
+        <v>122568906</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5123,10 +4939,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577765</v>
+        <v>577851</v>
       </c>
       <c r="R39" t="n">
-        <v>7047696</v>
+        <v>7047625</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5158,7 +4974,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5168,12 +4984,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5200,15 +5016,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566495</v>
+        <v>122568922</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5245,13 +5056,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577898</v>
+        <v>577858</v>
       </c>
       <c r="R40" t="n">
-        <v>7047638</v>
+        <v>7047635</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5280,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5290,12 +5101,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5310,27 +5121,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566696</v>
+        <v>122568941</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5358,7 +5164,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5367,10 +5173,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577752</v>
+        <v>577874</v>
       </c>
       <c r="R41" t="n">
-        <v>7047671</v>
+        <v>7047636</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5402,7 +5208,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5412,12 +5218,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5432,55 +5238,50 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566471</v>
+        <v>122566312</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5489,10 +5290,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577878</v>
+        <v>577901</v>
       </c>
       <c r="R42" t="n">
-        <v>7047667</v>
+        <v>7047598</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5524,7 +5325,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5534,12 +5335,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5554,27 +5350,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567415</v>
+        <v>122566271</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5582,27 +5373,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5611,13 +5402,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577665</v>
+        <v>577901</v>
       </c>
       <c r="R43" t="n">
-        <v>7047625</v>
+        <v>7047671</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5646,7 +5437,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5656,12 +5447,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5676,12 +5462,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 4827-2025 artfynd.xlsx
+++ b/artfynd/A 4827-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567286</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568013</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568145</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122565767</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566508</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566643</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567115</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568052</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568836</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566471</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566485</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566494</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2210,6 +2280,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566495</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2327,6 +2402,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566515</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2444,6 +2524,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566694</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2561,6 +2646,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566696</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2678,6 +2768,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566730</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2795,6 +2890,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566768</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567250</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3029,6 +3134,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567415</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3146,6 +3256,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567504</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3263,6 +3378,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567519</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3380,6 +3500,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567600</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3497,6 +3622,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567603</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3614,6 +3744,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567649</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3731,6 +3866,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567761</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3843,6 +3983,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567764</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3960,6 +4105,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567856</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4077,6 +4227,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568098</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4194,6 +4349,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568120</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4311,6 +4471,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568123</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4428,6 +4593,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568144</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4545,6 +4715,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568196</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4662,6 +4837,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568234</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4779,6 +4959,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568670</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4896,6 +5081,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568871</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5013,6 +5203,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568906</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5130,6 +5325,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568922</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5247,6 +5447,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568941</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5359,6 +5564,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566312</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5471,8 +5681,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566271</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>